--- a/public/data/hilton_resort_credit_v3.xlsx
+++ b/public/data/hilton_resort_credit_v3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="666">
   <si>
     <t>飯店名稱</t>
   </si>
@@ -1212,7 +1212,7 @@
     <t>Hilton Alexandria King's Ranch</t>
   </si>
   <si>
-    <t>—</t>
+    <t>https://www.tripadvisor.com/Hotel_Review-g295398-d7319768-Reviews-Hilton_Alexandria_King_s_Ranch-Alexandria_Alexandria_Governorate.html</t>
   </si>
   <si>
     <t>Hilton Anatole</t>
@@ -1221,6 +1221,9 @@
     <t>Dallas</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g55711-d98731-Reviews-Hilton_Anatole-Dallas_Texas.html</t>
+  </si>
+  <si>
     <t>Hilton Aruba Caribbean Resort &amp; Casino</t>
   </si>
   <si>
@@ -1272,6 +1275,9 @@
     <t>Colombia</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g297476-d300666-Reviews-Hilton_Cartagena_Hotel-Cartagena_Cartagena_District_Bolivar_Department.html</t>
+  </si>
+  <si>
     <t>Hilton Chicago/Oak Brook Hills Resort &amp; Conference Center</t>
   </si>
   <si>
@@ -1314,6 +1320,9 @@
     <t>Rockwall</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g56567-d1028763-Reviews-Hilton_Dallas_Rockwall_Lakefront-Rockwall_Texas.html</t>
+  </si>
+  <si>
     <t>Hilton Daytona Beach Oceanfront Resort</t>
   </si>
   <si>
@@ -1335,9 +1344,15 @@
     <t>Qatar</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g294009-d2216044-Reviews-Hilton_Doha-Doha.html</t>
+  </si>
+  <si>
     <t>Hilton Doha The Pearl</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g294009-d19106093-Reviews-Hilton_Doha_The_Pearl-Doha.html</t>
+  </si>
+  <si>
     <t>Hilton Dubai Jumeirah</t>
   </si>
   <si>
@@ -1347,6 +1362,9 @@
     <t>Hilton Dubai The Walk</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g295424-d2526254-Reviews-Hilton_Dubai_The_Walk-Dubai_Emirate_of_Dubai.html</t>
+  </si>
+  <si>
     <t>Hilton Fiji Beach Resort and Spa</t>
   </si>
   <si>
@@ -1362,6 +1380,9 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g198581-d273504-Reviews-Hilton_Frankfurt_Gravenbruch-Neu_Isenburg_Hesse.html</t>
+  </si>
+  <si>
     <t>Hilton Galveston Island Resort</t>
   </si>
   <si>
@@ -1389,6 +1410,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g297888-d308055-Reviews-Hilton_Gyeongju-Gyeongju_Gyeongsangbuk_do.html</t>
+  </si>
+  <si>
     <t>Hilton Hangzhou Qiandao Lake Resort</t>
   </si>
   <si>
@@ -1401,6 +1425,9 @@
     <t>Papeete</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g1190275-d23416500-Reviews-Hilton_Hotel_Tahiti-Faa_a_Tahiti_Society_Islands.html</t>
+  </si>
+  <si>
     <t>Hilton Hua Hin Resort &amp; Spa</t>
   </si>
   <si>
@@ -1419,12 +1446,18 @@
     <t>Hurghada</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g297549-d308117-Reviews-Hilton_Hurghada_Plaza-Hurghada_Red_Sea_and_Sinai.html</t>
+  </si>
+  <si>
     <t>Hilton La Jolla Torrey Pines</t>
   </si>
   <si>
     <t>La Jolla</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g32578-d218747-Reviews-Hilton_La_Jolla_Torrey_Pines-La_Jolla_San_Diego_California.html</t>
+  </si>
+  <si>
     <t>Hilton Lake Las Vegas Resort &amp; Spa</t>
   </si>
   <si>
@@ -1452,9 +1485,15 @@
     <t>Mallorca</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g580307-d500716-Reviews-Hilton_Mallorca_Galatzo-Peguera_Calvia_Majorca_Balearic_Islands.html</t>
+  </si>
+  <si>
     <t>Hilton Malta</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g227101-d227152-Reviews-Hilton_Malta-Saint_Julian_s_Island_of_Malta.html</t>
+  </si>
+  <si>
     <t>Hilton Marco Island Beach Resort</t>
   </si>
   <si>
@@ -1491,12 +1530,18 @@
     <t>Nanjing</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g294220-d26109625-Reviews-Hilton_Nanjing_Niushoushan-Nanjing_Jiangsu.html</t>
+  </si>
+  <si>
     <t>Hilton Ningbo Dongqian Lake</t>
   </si>
   <si>
     <t>Ningbo</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g297470-d11725429-Reviews-Hilton_Ningbo_Dongqian_Lake-Ningbo_Zhejiang.html</t>
+  </si>
+  <si>
     <t>Hilton Niseko Village</t>
   </si>
   <si>
@@ -1509,6 +1554,9 @@
     <t>Ocean City</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g41298-d601651-Reviews-Hilton_Ocean_City_Oceanfront_Suites-Ocean_City_Maryland.html</t>
+  </si>
+  <si>
     <t>Hilton Odawara Resort &amp; Spa</t>
   </si>
   <si>
@@ -1533,21 +1581,36 @@
     <t>Hilton Orlando</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g34515-d1382900-Reviews-Hilton_Orlando-Orlando_Florida.html</t>
+  </si>
+  <si>
     <t>Hilton Orlando Buena Vista Palace Disney Springs Area</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g23869903-d85979-Reviews-Hilton_Orlando_Buena_Vista_Palace_Disney_Springs_Area-Lake_Buena_Vista_Florida.html</t>
+  </si>
+  <si>
     <t>Hilton Orlando Lake Buena Vista - Disney Springs Area</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g23869903-d217366-Reviews-Hilton_Orlando_Lake_Buena_Vista_Disney_Springs_Area-Lake_Buena_Vista_Florida.html</t>
+  </si>
+  <si>
     <t>Hilton Palm Springs</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g32847-d77242-Reviews-Hilton_Palm_Springs-Palm_Springs_Greater_Palm_Springs_California.html</t>
+  </si>
+  <si>
     <t>Hilton Pattaya</t>
   </si>
   <si>
     <t>Pattaya</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g293919-d1876869-Reviews-or40-Hilton_Pattaya-Pattaya_Chonburi_Province.html</t>
+  </si>
+  <si>
     <t>Hilton Pensacola Beach</t>
   </si>
   <si>
@@ -1575,6 +1638,9 @@
     <t>Giza</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g8363967-d300671-Reviews-Hilton_Pyramids_Golf-6th_of_October_City_Giza_Governorate.html</t>
+  </si>
+  <si>
     <t>Hilton Queenstown Resort &amp; Spa</t>
   </si>
   <si>
@@ -1611,6 +1677,9 @@
     <t>Del Mar</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g32286-d501946-Reviews-Hilton_San_Diego_del_Mar-Del_Mar_California.html</t>
+  </si>
+  <si>
     <t>Hilton Sandestin Beach Golf Resort &amp; Spa</t>
   </si>
   <si>
@@ -1632,12 +1701,18 @@
     <t>Santa Fe</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g30700567-d1146058-Reviews-Hilton_Santa_Fe_Buffalo_Thunder-Cuyamungue_New_Mexico.html</t>
+  </si>
+  <si>
     <t>Hilton Santa Marta</t>
   </si>
   <si>
     <t>Santa Marta</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g297484-d25084426-Reviews-Hilton_Santa_Marta-Santa_Marta_Santa_Marta_Municipality_Magdalena_Department.html</t>
+  </si>
+  <si>
     <t>Hilton Sanya Yalong Bay Resort &amp; Spa</t>
   </si>
   <si>
@@ -1659,6 +1734,9 @@
     <t>Sorrento</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g187782-d231243-Reviews-Hilton_Sorrento_Palace-Sorrento_Province_of_Naples_Campania.html</t>
+  </si>
+  <si>
     <t>Hilton Swinoujscie Resort &amp; Spa</t>
   </si>
   <si>
@@ -1719,6 +1797,9 @@
     <t>Yuxi</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g1575828-d7927386-Reviews-Hilton_Yuxi_Fuxian_Lake-Chengjiang_County_Yunnan.html</t>
+  </si>
+  <si>
     <t>Las Vegas Hilton at Resorts World</t>
   </si>
   <si>
@@ -1731,9 +1812,15 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g255072-d1853238-Reviews-Hilton_Surfers_Paradise_Hotel_Residences-Surfers_Paradise_Gold_Coast_Queensland.html</t>
+  </si>
+  <si>
     <t>The Condado Plaza Hotel</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g147320-d150443-Reviews-The_Condado_Plaza_Hotel-San_Juan_Puerto_Rico.html</t>
+  </si>
+  <si>
     <t>The Inverness Denver, a Hilton Golf &amp; Spa Resort</t>
   </si>
   <si>
@@ -1743,6 +1830,9 @@
     <t>The Lodge at Gulf State Park, a Hilton Hotel</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g30582-d14084829-Reviews-The_Lodge_At_Gulf_State_Park_A_Hilton_Hotel-Gulf_Shores_Alabama.html</t>
+  </si>
+  <si>
     <t>The Waterfront Beach Resort, a Hilton Hotel</t>
   </si>
   <si>
@@ -1764,6 +1854,9 @@
     <t>LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g31310-d115484-Reviews-Arizona_Biltmore_LXR_Hotels_Resorts-Phoenix_Arizona.html</t>
+  </si>
+  <si>
     <t>Beach Village at The Del, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
@@ -1776,27 +1869,48 @@
     <t>Katara Hills Doha, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g294009-d25173967-Reviews-Katara_Hills_Doha_Lxr_Hotels_Resorts-Doha.html</t>
+  </si>
+  <si>
     <t>Mango House Seychelles, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g488116-d23118132-Reviews-Mango_House_Seychelles_LXR_Hotels_Resorts-Baie_Lazare_Mahe_Island.html</t>
+  </si>
+  <si>
     <t>Maysan Doha, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g1592998-d25173962-Reviews-or20-Maysan_Doha_LXR_Hotels_Resorts-Al_Rayyan.html</t>
+  </si>
+  <si>
     <t>ROKU KYOTO, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
     <t>Kyoto</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g298564-d23331390-Reviews-ROKU_KYOTO_LXR_Hotels_Resorts-Kyoto_Kyoto_Prefecture_Kinki.html</t>
+  </si>
+  <si>
     <t>Shore House at The Del, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.hilton.com/en/hotels/sanrhol-shore-house-at-the-del/</t>
+  </si>
+  <si>
     <t>Susona Bodrum, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g298663-d20483728-Reviews-Susona_Bodrum_LXR_Hotels_Resorts-Torba_Bodrum_District_Mugla_Province_Turkish_Aegean_.html</t>
+  </si>
+  <si>
     <t>Umana Bali, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g1219108-d887047-Reviews-Umana_Bali_LXR_Hotels_Resorts-Ungasan_Bukit_Peninsula_Bali.html</t>
+  </si>
+  <si>
     <t>Zemi Beach House, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
@@ -1813,6 +1927,9 @@
   </si>
   <si>
     <t>Signia by Hilton Orlando Bonnet Creek</t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g34515-d1308392-Reviews-Signia_By_Hilton_Orlando_An_Official_Walt_Disney_WorldR_Hotel-Orlando_Florida.html</t>
   </si>
   <si>
     <t>Fuwairit Kite Beach, Tapestry Collection by Hilton</t>
@@ -1909,7 +2026,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -2032,6 +2149,12 @@
     <font>
       <u/>
       <sz val="10.0"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
@@ -2043,11 +2166,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10.0"/>
-      <color rgb="FF999999"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color rgb="FF999999"/>
       <name val="Arial"/>
@@ -2073,6 +2191,12 @@
     <font>
       <u/>
       <sz val="10.0"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
       <color rgb="FF0B6E4F"/>
       <name val="Arial"/>
     </font>
@@ -2086,6 +2210,12 @@
       <u/>
       <sz val="10.0"/>
       <color rgb="FF0B6E4F"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF999999"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -2329,23 +2459,23 @@
     <xf borderId="1" fillId="8" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="8" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="9" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2368,10 +2498,10 @@
     <xf borderId="1" fillId="11" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="1" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="11" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="11" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2380,14 +2510,14 @@
     <xf borderId="1" fillId="12" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="12" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="12" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="12" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="12" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="13" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2395,10 +2525,10 @@
     <xf borderId="1" fillId="13" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="13" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="13" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="13" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="14" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2407,17 +2537,17 @@
     <xf borderId="1" fillId="14" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="14" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="14" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="14" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="14" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="36" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="35" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="37" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -6729,7 +6859,7 @@
       <c r="H141" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I141" s="30" t="s">
+      <c r="I141" s="31" t="s">
         <v>317</v>
       </c>
     </row>
@@ -7691,202 +7821,202 @@
       </c>
     </row>
     <row r="175" ht="18.0" hidden="1" customHeight="1">
-      <c r="A175" s="31" t="s">
+      <c r="A175" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="B175" s="31" t="s">
+      <c r="B175" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C175" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D175" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E175" s="32">
+      <c r="C175" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D175" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E175" s="33">
         <v>26.1224</v>
       </c>
-      <c r="F175" s="32">
+      <c r="F175" s="33">
         <v>-80.1034</v>
       </c>
-      <c r="G175" s="31" t="s">
+      <c r="G175" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H175" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I175" s="34" t="s">
+      <c r="H175" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I175" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="176" ht="18.0" hidden="1" customHeight="1">
-      <c r="A176" s="31" t="s">
+      <c r="A176" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="B176" s="31" t="s">
+      <c r="B176" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="C176" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D176" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E176" s="32">
+      <c r="C176" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D176" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E176" s="33">
         <v>33.1581</v>
       </c>
-      <c r="F176" s="32">
+      <c r="F176" s="33">
         <v>-117.3506</v>
       </c>
-      <c r="G176" s="31" t="s">
+      <c r="G176" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H176" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I176" s="34" t="s">
+      <c r="H176" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I176" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="177" ht="18.0" customHeight="1">
-      <c r="A177" s="31" t="s">
+      <c r="A177" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="B177" s="31" t="s">
+      <c r="B177" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="C177" s="31" t="s">
+      <c r="C177" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="D177" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E177" s="32">
+      <c r="D177" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E177" s="33">
         <v>18.4655</v>
       </c>
-      <c r="F177" s="32">
+      <c r="F177" s="33">
         <v>-66.1057</v>
       </c>
-      <c r="G177" s="31" t="s">
+      <c r="G177" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H177" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I177" s="35" t="s">
+      <c r="H177" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I177" s="36" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="178" ht="18.0" hidden="1" customHeight="1">
-      <c r="A178" s="31" t="s">
+      <c r="A178" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="B178" s="31" t="s">
+      <c r="B178" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="C178" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D178" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E178" s="32">
+      <c r="C178" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D178" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E178" s="33">
         <v>32.37</v>
       </c>
-      <c r="F178" s="32">
+      <c r="F178" s="33">
         <v>-110.9747</v>
       </c>
-      <c r="G178" s="31" t="s">
+      <c r="G178" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H178" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I178" s="34" t="s">
+      <c r="H178" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I178" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="179" ht="18.0" customHeight="1">
-      <c r="A179" s="31" t="s">
+      <c r="A179" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="B179" s="31" t="s">
+      <c r="B179" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C179" s="31" t="s">
+      <c r="C179" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D179" s="31" t="s">
+      <c r="D179" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E179" s="32">
+      <c r="E179" s="33">
         <v>24.4707</v>
       </c>
-      <c r="F179" s="32">
+      <c r="F179" s="33">
         <v>54.6033</v>
       </c>
-      <c r="G179" s="31" t="s">
+      <c r="G179" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H179" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I179" s="35" t="s">
+      <c r="H179" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I179" s="36" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="180" ht="18.0" customHeight="1">
-      <c r="A180" s="31" t="s">
+      <c r="A180" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="B180" s="31" t="s">
+      <c r="B180" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="C180" s="31" t="s">
+      <c r="C180" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D180" s="31" t="s">
+      <c r="D180" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E180" s="32">
+      <c r="E180" s="33">
         <v>31.2001</v>
       </c>
-      <c r="F180" s="32">
+      <c r="F180" s="33">
         <v>29.9187</v>
       </c>
-      <c r="G180" s="31" t="s">
+      <c r="G180" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H180" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I180" s="35" t="s">
+      <c r="H180" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I180" s="36" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="181" ht="18.0" customHeight="1">
-      <c r="A181" s="31" t="s">
+      <c r="A181" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="B181" s="31" t="s">
+      <c r="B181" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="C181" s="31" t="s">
+      <c r="C181" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D181" s="31" t="s">
+      <c r="D181" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E181" s="32">
+      <c r="E181" s="33">
         <v>31.2001</v>
       </c>
-      <c r="F181" s="32">
+      <c r="F181" s="33">
         <v>29.9187</v>
       </c>
-      <c r="G181" s="31" t="s">
+      <c r="G181" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H181" s="33" t="s">
+      <c r="H181" s="34" t="s">
         <v>7</v>
       </c>
       <c r="I181" s="36" t="s">
@@ -7894,2940 +8024,2940 @@
       </c>
     </row>
     <row r="182" ht="18.0" customHeight="1">
-      <c r="A182" s="31" t="s">
+      <c r="A182" s="32" t="s">
         <v>398</v>
       </c>
-      <c r="B182" s="31" t="s">
+      <c r="B182" s="32" t="s">
         <v>399</v>
       </c>
-      <c r="C182" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D182" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E182" s="32">
+      <c r="C182" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D182" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E182" s="33">
         <v>32.7877</v>
       </c>
-      <c r="F182" s="32">
+      <c r="F182" s="33">
         <v>-96.8286</v>
       </c>
-      <c r="G182" s="31" t="s">
+      <c r="G182" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H182" s="33" t="s">
+      <c r="H182" s="34" t="s">
         <v>7</v>
       </c>
       <c r="I182" s="36" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="183" ht="18.0" hidden="1" customHeight="1">
-      <c r="A183" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="B183" s="31" t="s">
+      <c r="A183" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B183" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C183" s="31" t="s">
+      <c r="C183" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="D183" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E183" s="32">
+      <c r="D183" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E183" s="33">
         <v>12.5667</v>
       </c>
-      <c r="F183" s="32">
+      <c r="F183" s="33">
         <v>-70.0167</v>
       </c>
-      <c r="G183" s="31" t="s">
+      <c r="G183" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H183" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I183" s="34" t="s">
+      <c r="H183" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I183" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="184" ht="18.0" hidden="1" customHeight="1">
-      <c r="A184" s="31" t="s">
-        <v>401</v>
-      </c>
-      <c r="B184" s="31" t="s">
+      <c r="A184" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="B184" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C184" s="31" t="s">
+      <c r="C184" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D184" s="31" t="s">
+      <c r="D184" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E184" s="32">
+      <c r="E184" s="33">
         <v>-8.8291</v>
       </c>
-      <c r="F184" s="32">
+      <c r="F184" s="33">
         <v>115.213</v>
       </c>
-      <c r="G184" s="31" t="s">
+      <c r="G184" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H184" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I184" s="34" t="s">
+      <c r="H184" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I184" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="185" ht="18.0" hidden="1" customHeight="1">
-      <c r="A185" s="31" t="s">
-        <v>402</v>
-      </c>
-      <c r="B185" s="31" t="s">
+      <c r="A185" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="C185" s="31" t="s">
+      <c r="B185" s="32" t="s">
+        <v>404</v>
+      </c>
+      <c r="C185" s="32" t="s">
         <v>324</v>
       </c>
-      <c r="D185" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E185" s="32">
+      <c r="D185" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E185" s="33">
         <v>13.0667</v>
       </c>
-      <c r="F185" s="32">
+      <c r="F185" s="33">
         <v>-59.6167</v>
       </c>
-      <c r="G185" s="31" t="s">
+      <c r="G185" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H185" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I185" s="34" t="s">
+      <c r="H185" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I185" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="186" ht="18.0" hidden="1" customHeight="1">
-      <c r="A186" s="31" t="s">
-        <v>404</v>
-      </c>
-      <c r="B186" s="31" t="s">
+      <c r="A186" s="32" t="s">
         <v>405</v>
       </c>
-      <c r="C186" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D186" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E186" s="32">
+      <c r="B186" s="32" t="s">
+        <v>406</v>
+      </c>
+      <c r="C186" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D186" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E186" s="33">
         <v>32.1837</v>
       </c>
-      <c r="F186" s="32">
+      <c r="F186" s="33">
         <v>-80.7526</v>
       </c>
-      <c r="G186" s="31" t="s">
+      <c r="G186" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H186" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I186" s="34" t="s">
+      <c r="H186" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I186" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="187" ht="18.0" hidden="1" customHeight="1">
-      <c r="A187" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="B187" s="31" t="s">
+      <c r="A187" s="32" t="s">
+        <v>407</v>
+      </c>
+      <c r="B187" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C187" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D187" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E187" s="32">
+      <c r="C187" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D187" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E187" s="33">
         <v>25.78</v>
       </c>
-      <c r="F187" s="32">
+      <c r="F187" s="33">
         <v>-80.13</v>
       </c>
-      <c r="G187" s="31" t="s">
+      <c r="G187" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H187" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I187" s="34" t="s">
+      <c r="H187" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I187" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="188" ht="18.0" hidden="1" customHeight="1">
-      <c r="A188" s="31" t="s">
-        <v>407</v>
-      </c>
-      <c r="B188" s="31" t="s">
+      <c r="A188" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="B188" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C188" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D188" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E188" s="32">
+      <c r="C188" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D188" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E188" s="33">
         <v>25.7993</v>
       </c>
-      <c r="F188" s="32">
+      <c r="F188" s="33">
         <v>-80.1319</v>
       </c>
-      <c r="G188" s="31" t="s">
+      <c r="G188" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H188" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I188" s="34" t="s">
+      <c r="H188" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I188" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="189" ht="18.0" hidden="1" customHeight="1">
-      <c r="A189" s="31" t="s">
-        <v>408</v>
-      </c>
-      <c r="B189" s="31" t="s">
+      <c r="A189" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="C189" s="31" t="s">
+      <c r="B189" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="D189" s="31" t="s">
+      <c r="C189" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="D189" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="E189" s="32">
+      <c r="E189" s="33">
         <v>16.7333</v>
       </c>
-      <c r="F189" s="32">
+      <c r="F189" s="33">
         <v>-22.9333</v>
       </c>
-      <c r="G189" s="31" t="s">
+      <c r="G189" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H189" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I189" s="34" t="s">
+      <c r="H189" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I189" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="190" ht="18.0" hidden="1" customHeight="1">
-      <c r="A190" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B190" s="31" t="s">
+      <c r="A190" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="C190" s="31" t="s">
+      <c r="B190" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="C190" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D190" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E190" s="32">
+      <c r="D190" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E190" s="33">
         <v>21.1619</v>
       </c>
-      <c r="F190" s="32">
+      <c r="F190" s="33">
         <v>-86.8515</v>
       </c>
-      <c r="G190" s="31" t="s">
+      <c r="G190" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H190" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I190" s="34" t="s">
+      <c r="H190" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I190" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="191" ht="18.0" hidden="1" customHeight="1">
-      <c r="A191" s="31" t="s">
+      <c r="A191" s="32" t="s">
+        <v>414</v>
+      </c>
+      <c r="B191" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="B191" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="C191" s="31" t="s">
+      <c r="C191" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D191" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E191" s="32">
+      <c r="D191" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E191" s="33">
         <v>21.1619</v>
       </c>
-      <c r="F191" s="32">
+      <c r="F191" s="33">
         <v>-86.8515</v>
       </c>
-      <c r="G191" s="31" t="s">
+      <c r="G191" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H191" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I191" s="34" t="s">
+      <c r="H191" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I191" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="192" ht="18.0" customHeight="1">
-      <c r="A192" s="31" t="s">
-        <v>414</v>
-      </c>
-      <c r="B192" s="31" t="s">
+      <c r="A192" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="C192" s="31" t="s">
+      <c r="B192" s="32" t="s">
         <v>416</v>
       </c>
-      <c r="D192" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E192" s="32">
+      <c r="C192" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="D192" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E192" s="33">
         <v>10.3932</v>
       </c>
-      <c r="F192" s="32">
+      <c r="F192" s="33">
         <v>-75.4832</v>
       </c>
-      <c r="G192" s="31" t="s">
+      <c r="G192" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H192" s="33" t="s">
+      <c r="H192" s="34" t="s">
         <v>7</v>
       </c>
       <c r="I192" s="36" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
     </row>
     <row r="193" ht="18.0" hidden="1" customHeight="1">
-      <c r="A193" s="31" t="s">
+      <c r="A193" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="B193" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="C193" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D193" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E193" s="33">
+        <v>41.8508</v>
+      </c>
+      <c r="F193" s="33">
+        <v>-87.9401</v>
+      </c>
+      <c r="G193" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H193" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I193" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" ht="18.0" hidden="1" customHeight="1">
+      <c r="A194" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="B194" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="C194" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="D194" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E194" s="33">
+        <v>15.179</v>
+      </c>
+      <c r="F194" s="33">
+        <v>120.539</v>
+      </c>
+      <c r="G194" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H194" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I194" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" ht="18.0" hidden="1" customHeight="1">
+      <c r="A195" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B195" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C195" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D195" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E195" s="33">
+        <v>27.9768</v>
+      </c>
+      <c r="F195" s="33">
+        <v>-82.8272</v>
+      </c>
+      <c r="G195" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H195" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I195" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="196" ht="18.0" hidden="1" customHeight="1">
+      <c r="A196" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="C196" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D196" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" s="33">
+        <v>36.7333</v>
+      </c>
+      <c r="F196" s="33">
+        <v>28.7667</v>
+      </c>
+      <c r="G196" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H196" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I196" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" ht="18.0" hidden="1" customHeight="1">
+      <c r="A197" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="B197" s="32" t="s">
+        <v>428</v>
+      </c>
+      <c r="C197" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D197" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E197" s="33">
+        <v>25.6941</v>
+      </c>
+      <c r="F197" s="33">
+        <v>100.16</v>
+      </c>
+      <c r="G197" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H197" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I197" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" ht="18.0" hidden="1" customHeight="1">
+      <c r="A198" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="B198" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="C198" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D198" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E198" s="33">
+        <v>38.914</v>
+      </c>
+      <c r="F198" s="33">
+        <v>121.6147</v>
+      </c>
+      <c r="G198" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H198" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I198" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199" ht="18.0" customHeight="1">
+      <c r="A199" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="B199" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="C199" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D199" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E199" s="33">
+        <v>32.93</v>
+      </c>
+      <c r="F199" s="33">
+        <v>-96.4597</v>
+      </c>
+      <c r="G199" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H199" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I199" s="36" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="200" ht="18.0" hidden="1" customHeight="1">
+      <c r="A200" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="B200" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="C200" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D200" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E200" s="33">
+        <v>29.2108</v>
+      </c>
+      <c r="F200" s="33">
+        <v>-81.0228</v>
+      </c>
+      <c r="G200" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H200" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I200" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" ht="18.0" hidden="1" customHeight="1">
+      <c r="A201" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="B201" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="C201" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="D201" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E201" s="33">
+        <v>31.7667</v>
+      </c>
+      <c r="F201" s="33">
+        <v>35.5833</v>
+      </c>
+      <c r="G201" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H201" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I201" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" ht="18.0" customHeight="1">
+      <c r="A202" s="32" t="s">
+        <v>438</v>
+      </c>
+      <c r="B202" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="C202" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="D202" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E202" s="33">
+        <v>25.2854</v>
+      </c>
+      <c r="F202" s="33">
+        <v>51.531</v>
+      </c>
+      <c r="G202" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H202" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I202" s="36" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="203" ht="18.0" customHeight="1">
+      <c r="A203" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="B203" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="C203" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="D203" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E203" s="33">
+        <v>25.3725</v>
+      </c>
+      <c r="F203" s="33">
+        <v>51.5505</v>
+      </c>
+      <c r="G203" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H203" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I203" s="36" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="204" ht="18.0" hidden="1" customHeight="1">
+      <c r="A204" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="B204" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C204" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D204" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E204" s="33">
+        <v>25.097</v>
+      </c>
+      <c r="F204" s="33">
+        <v>55.1447</v>
+      </c>
+      <c r="G204" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H204" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I204" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="205" ht="18.0" hidden="1" customHeight="1">
+      <c r="A205" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="B205" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C205" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D205" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E205" s="33">
+        <v>25.1124</v>
+      </c>
+      <c r="F205" s="33">
+        <v>55.139</v>
+      </c>
+      <c r="G205" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H205" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I205" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206" ht="18.0" customHeight="1">
+      <c r="A206" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="B206" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C206" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D206" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E206" s="33">
+        <v>25.0781</v>
+      </c>
+      <c r="F206" s="33">
+        <v>55.1305</v>
+      </c>
+      <c r="G206" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H206" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I206" s="36" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="207" ht="18.0" hidden="1" customHeight="1">
+      <c r="A207" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="B207" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C207" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D207" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E207" s="33">
+        <v>-17.7833</v>
+      </c>
+      <c r="F207" s="33">
+        <v>177.4167</v>
+      </c>
+      <c r="G207" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H207" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I207" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="208" ht="18.0" hidden="1" customHeight="1">
+      <c r="A208" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="B208" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D208" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E208" s="33">
+        <v>26.1224</v>
+      </c>
+      <c r="F208" s="33">
+        <v>-80.1034</v>
+      </c>
+      <c r="G208" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H208" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I208" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" ht="18.0" customHeight="1">
+      <c r="A209" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="B209" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C209" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="D209" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" s="33">
+        <v>50.0259</v>
+      </c>
+      <c r="F209" s="33">
+        <v>8.835</v>
+      </c>
+      <c r="G209" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H209" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I209" s="36" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="210" ht="18.0" hidden="1" customHeight="1">
+      <c r="A210" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="B210" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="C210" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D210" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E210" s="33">
+        <v>29.2108</v>
+      </c>
+      <c r="F210" s="33">
+        <v>-94.8639</v>
+      </c>
+      <c r="G210" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H210" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I210" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="211" ht="18.0" hidden="1" customHeight="1">
+      <c r="A211" s="32" t="s">
+        <v>456</v>
+      </c>
+      <c r="B211" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C211" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D211" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E211" s="33">
+        <v>15.4989</v>
+      </c>
+      <c r="F211" s="33">
+        <v>73.8278</v>
+      </c>
+      <c r="G211" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H211" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I211" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="212" ht="18.0" hidden="1" customHeight="1">
+      <c r="A212" s="32" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="32" t="s">
+        <v>458</v>
+      </c>
+      <c r="C212" s="32" t="s">
+        <v>459</v>
+      </c>
+      <c r="D212" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E212" s="33">
+        <v>13.5135</v>
+      </c>
+      <c r="F212" s="33">
+        <v>144.7981</v>
+      </c>
+      <c r="G212" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H212" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I212" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" ht="18.0" customHeight="1">
+      <c r="A213" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="B213" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="C213" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="D213" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E213" s="33">
+        <v>35.8562</v>
+      </c>
+      <c r="F213" s="33">
+        <v>129.225</v>
+      </c>
+      <c r="G213" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H213" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I213" s="36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="214" ht="18.0" hidden="1" customHeight="1">
+      <c r="A214" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="B214" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C214" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D214" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E214" s="33">
+        <v>29.606</v>
+      </c>
+      <c r="F214" s="33">
+        <v>118.996</v>
+      </c>
+      <c r="G214" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H214" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I214" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="215" ht="18.0" hidden="1" customHeight="1">
+      <c r="A215" s="32" t="s">
+        <v>465</v>
+      </c>
+      <c r="B215" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="C215" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D215" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E215" s="33">
+        <v>21.2793</v>
+      </c>
+      <c r="F215" s="33">
+        <v>-157.8389</v>
+      </c>
+      <c r="G215" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H215" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I215" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216" ht="18.0" customHeight="1">
+      <c r="A216" s="32" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" s="32" t="s">
+        <v>467</v>
+      </c>
+      <c r="C216" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D216" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E216" s="33">
+        <v>-17.5334</v>
+      </c>
+      <c r="F216" s="33">
+        <v>-149.5693</v>
+      </c>
+      <c r="G216" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H216" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I216" s="36" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="217" ht="18.0" hidden="1" customHeight="1">
+      <c r="A217" s="32" t="s">
+        <v>469</v>
+      </c>
+      <c r="B217" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="C217" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D217" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E217" s="33">
+        <v>12.5667</v>
+      </c>
+      <c r="F217" s="33">
+        <v>99.9667</v>
+      </c>
+      <c r="G217" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H217" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I217" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="218" ht="18.0" hidden="1" customHeight="1">
+      <c r="A218" s="32" t="s">
+        <v>471</v>
+      </c>
+      <c r="B218" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="C218" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D218" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E218" s="33">
+        <v>23.8833</v>
+      </c>
+      <c r="F218" s="33">
+        <v>114.4167</v>
+      </c>
+      <c r="G218" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H218" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I218" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219" ht="18.0" customHeight="1">
+      <c r="A219" s="32" t="s">
+        <v>473</v>
+      </c>
+      <c r="B219" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="C219" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D219" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E219" s="33">
+        <v>27.2579</v>
+      </c>
+      <c r="F219" s="33">
+        <v>33.8116</v>
+      </c>
+      <c r="G219" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H219" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I219" s="36" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="220" ht="18.0" customHeight="1">
+      <c r="A220" s="32" t="s">
+        <v>476</v>
+      </c>
+      <c r="B220" s="32" t="s">
+        <v>477</v>
+      </c>
+      <c r="C220" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D220" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E220" s="33">
+        <v>32.905</v>
+      </c>
+      <c r="F220" s="33">
+        <v>-117.234</v>
+      </c>
+      <c r="G220" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H220" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I220" s="36" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="221" ht="18.0" hidden="1" customHeight="1">
+      <c r="A221" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="B221" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="C221" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D221" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E221" s="33">
+        <v>36.0553</v>
+      </c>
+      <c r="F221" s="33">
+        <v>-114.9418</v>
+      </c>
+      <c r="G221" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H221" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I221" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" ht="18.0" hidden="1" customHeight="1">
+      <c r="A222" s="32" t="s">
+        <v>481</v>
+      </c>
+      <c r="B222" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C222" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D222" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E222" s="33">
+        <v>22.8906</v>
+      </c>
+      <c r="F222" s="33">
+        <v>-109.9167</v>
+      </c>
+      <c r="G222" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H222" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I222" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="223" ht="18.0" hidden="1" customHeight="1">
+      <c r="A223" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="B223" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="C223" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D223" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E223" s="33">
+        <v>25.6872</v>
+      </c>
+      <c r="F223" s="33">
+        <v>32.6396</v>
+      </c>
+      <c r="G223" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H223" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I223" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" ht="18.0" hidden="1" customHeight="1">
+      <c r="A224" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="B224" s="32" t="s">
+        <v>485</v>
+      </c>
+      <c r="C224" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D224" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E224" s="33">
+        <v>4.25</v>
+      </c>
+      <c r="F224" s="33">
+        <v>73.5833</v>
+      </c>
+      <c r="G224" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H224" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I224" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="225" ht="18.0" customHeight="1">
+      <c r="A225" s="32" t="s">
+        <v>486</v>
+      </c>
+      <c r="B225" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="C225" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D225" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E225" s="33">
+        <v>39.55</v>
+      </c>
+      <c r="F225" s="33">
+        <v>2.65</v>
+      </c>
+      <c r="G225" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H225" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I225" s="36" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="226" ht="18.0" customHeight="1">
+      <c r="A226" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="B226" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C226" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D226" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E226" s="33">
+        <v>35.9167</v>
+      </c>
+      <c r="F226" s="33">
+        <v>14.4833</v>
+      </c>
+      <c r="G226" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H226" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I226" s="36" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="227" ht="18.0" hidden="1" customHeight="1">
+      <c r="A227" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="B227" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="C227" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D227" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E227" s="33">
+        <v>25.9423</v>
+      </c>
+      <c r="F227" s="33">
+        <v>-81.7201</v>
+      </c>
+      <c r="G227" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H227" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I227" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228" ht="18.0" hidden="1" customHeight="1">
+      <c r="A228" s="32" t="s">
+        <v>493</v>
+      </c>
+      <c r="B228" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="C228" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D228" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E228" s="33">
+        <v>25.0667</v>
+      </c>
+      <c r="F228" s="33">
+        <v>34.8833</v>
+      </c>
+      <c r="G228" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H228" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I228" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229" ht="18.0" hidden="1" customHeight="1">
+      <c r="A229" s="32" t="s">
+        <v>495</v>
+      </c>
+      <c r="B229" s="32" t="s">
+        <v>496</v>
+      </c>
+      <c r="C229" s="32" t="s">
+        <v>497</v>
+      </c>
+      <c r="D229" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229" s="33">
+        <v>-20.2833</v>
+      </c>
+      <c r="F229" s="33">
+        <v>57.3667</v>
+      </c>
+      <c r="G229" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H229" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I229" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230" ht="18.0" hidden="1" customHeight="1">
+      <c r="A230" s="32" t="s">
+        <v>498</v>
+      </c>
+      <c r="B230" s="32" t="s">
+        <v>499</v>
+      </c>
+      <c r="C230" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="D230" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E230" s="33">
+        <v>-17.5</v>
+      </c>
+      <c r="F230" s="33">
+        <v>-149.8333</v>
+      </c>
+      <c r="G230" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H230" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I230" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="231" ht="18.0" hidden="1" customHeight="1">
+      <c r="A231" s="32" t="s">
+        <v>500</v>
+      </c>
+      <c r="B231" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="C231" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D231" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E231" s="33">
+        <v>33.7041</v>
+      </c>
+      <c r="F231" s="33">
+        <v>-78.8764</v>
+      </c>
+      <c r="G231" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H231" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I231" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="232" ht="18.0" customHeight="1">
+      <c r="A232" s="32" t="s">
+        <v>501</v>
+      </c>
+      <c r="B232" s="32" t="s">
+        <v>502</v>
+      </c>
+      <c r="C232" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D232" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E232" s="33">
+        <v>31.67</v>
+      </c>
+      <c r="F232" s="33">
+        <v>118.83</v>
+      </c>
+      <c r="G232" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H232" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I232" s="36" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="233" ht="18.0" customHeight="1">
+      <c r="A233" s="32" t="s">
+        <v>504</v>
+      </c>
+      <c r="B233" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="C233" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D233" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E233" s="33">
+        <v>29.8047</v>
+      </c>
+      <c r="F233" s="33">
+        <v>121.5654</v>
+      </c>
+      <c r="G233" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H233" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I233" s="36" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="234" ht="18.0" hidden="1" customHeight="1">
+      <c r="A234" s="32" t="s">
+        <v>507</v>
+      </c>
+      <c r="B234" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="C234" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D234" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E234" s="33">
+        <v>42.7896</v>
+      </c>
+      <c r="F234" s="33">
+        <v>140.6864</v>
+      </c>
+      <c r="G234" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H234" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I234" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="235" ht="18.0" customHeight="1">
+      <c r="A235" s="32" t="s">
+        <v>509</v>
+      </c>
+      <c r="B235" s="32" t="s">
+        <v>510</v>
+      </c>
+      <c r="C235" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D235" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E235" s="33">
+        <v>38.3365</v>
+      </c>
+      <c r="F235" s="33">
+        <v>-75.0849</v>
+      </c>
+      <c r="G235" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H235" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I235" s="36" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="236" ht="18.0" hidden="1" customHeight="1">
+      <c r="A236" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="B236" s="32" t="s">
+        <v>513</v>
+      </c>
+      <c r="C236" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D236" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E236" s="33">
+        <v>35.2553</v>
+      </c>
+      <c r="F236" s="33">
+        <v>139.15</v>
+      </c>
+      <c r="G236" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H236" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I236" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" ht="18.0" hidden="1" customHeight="1">
+      <c r="A237" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="B237" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="C237" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D237" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E237" s="33">
+        <v>26.3167</v>
+      </c>
+      <c r="F237" s="33">
+        <v>127.75</v>
+      </c>
+      <c r="G237" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H237" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I237" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="238" ht="18.0" hidden="1" customHeight="1">
+      <c r="A238" s="32" t="s">
+        <v>515</v>
+      </c>
+      <c r="B238" s="32" t="s">
+        <v>516</v>
+      </c>
+      <c r="C238" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D238" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E238" s="33">
+        <v>24.8056</v>
+      </c>
+      <c r="F238" s="33">
+        <v>125.2814</v>
+      </c>
+      <c r="G238" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H238" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I238" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="239" ht="18.0" hidden="1" customHeight="1">
+      <c r="A239" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="B239" s="32" t="s">
+        <v>518</v>
+      </c>
+      <c r="C239" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D239" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E239" s="33">
+        <v>26.6333</v>
+      </c>
+      <c r="F239" s="33">
+        <v>127.8667</v>
+      </c>
+      <c r="G239" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H239" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I239" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="240" ht="18.0" customHeight="1">
+      <c r="A240" s="32" t="s">
+        <v>519</v>
+      </c>
+      <c r="B240" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C240" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D240" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E240" s="33">
+        <v>28.4177</v>
+      </c>
+      <c r="F240" s="33">
+        <v>-81.5812</v>
+      </c>
+      <c r="G240" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H240" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I240" s="36" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="241" ht="18.0" customHeight="1">
+      <c r="A241" s="32" t="s">
+        <v>521</v>
+      </c>
+      <c r="B241" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C241" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D241" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E241" s="33">
+        <v>28.3694</v>
+      </c>
+      <c r="F241" s="33">
+        <v>-81.516</v>
+      </c>
+      <c r="G241" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H241" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I241" s="36" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="242" ht="18.0" customHeight="1">
+      <c r="A242" s="32" t="s">
+        <v>523</v>
+      </c>
+      <c r="B242" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C242" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D242" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E242" s="33">
+        <v>28.3694</v>
+      </c>
+      <c r="F242" s="33">
+        <v>-81.516</v>
+      </c>
+      <c r="G242" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H242" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I242" s="36" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="243" ht="18.0" customHeight="1">
+      <c r="A243" s="32" t="s">
+        <v>525</v>
+      </c>
+      <c r="B243" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C243" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D243" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E243" s="33">
+        <v>33.8303</v>
+      </c>
+      <c r="F243" s="33">
+        <v>-116.5453</v>
+      </c>
+      <c r="G243" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H243" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I243" s="36" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="244" ht="18.0" customHeight="1">
+      <c r="A244" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="B244" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="C244" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D244" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E244" s="33">
+        <v>12.9236</v>
+      </c>
+      <c r="F244" s="33">
+        <v>100.8825</v>
+      </c>
+      <c r="G244" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H244" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I244" s="36" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="245" ht="18.0" hidden="1" customHeight="1">
+      <c r="A245" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="B245" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="C245" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D245" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E245" s="33">
+        <v>30.3344</v>
+      </c>
+      <c r="F245" s="33">
+        <v>-87.1627</v>
+      </c>
+      <c r="G245" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H245" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I245" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="246" ht="18.0" hidden="1" customHeight="1">
+      <c r="A246" s="32" t="s">
+        <v>532</v>
+      </c>
+      <c r="B246" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C246" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D246" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E246" s="33">
+        <v>33.6589</v>
+      </c>
+      <c r="F246" s="33">
+        <v>-111.8743</v>
+      </c>
+      <c r="G246" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H246" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I246" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="247" ht="18.0" hidden="1" customHeight="1">
+      <c r="A247" s="32" t="s">
+        <v>534</v>
+      </c>
+      <c r="B247" s="32" t="s">
+        <v>533</v>
+      </c>
+      <c r="C247" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D247" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E247" s="33">
+        <v>33.6589</v>
+      </c>
+      <c r="F247" s="33">
+        <v>-111.8743</v>
+      </c>
+      <c r="G247" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H247" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I247" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="248" ht="18.0" hidden="1" customHeight="1">
+      <c r="A248" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="B248" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="C248" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="D248" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E248" s="33">
+        <v>17.9995</v>
+      </c>
+      <c r="F248" s="33">
+        <v>-66.6141</v>
+      </c>
+      <c r="G248" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H248" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I248" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="249" ht="18.0" customHeight="1">
+      <c r="A249" s="32" t="s">
+        <v>537</v>
+      </c>
+      <c r="B249" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="C249" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D249" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E249" s="33">
+        <v>29.9792</v>
+      </c>
+      <c r="F249" s="33">
+        <v>31.1342</v>
+      </c>
+      <c r="G249" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H249" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I249" s="36" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="250" ht="18.0" hidden="1" customHeight="1">
+      <c r="A250" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="B250" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="C250" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="D250" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E250" s="33">
+        <v>-45.0312</v>
+      </c>
+      <c r="F250" s="33">
+        <v>168.6626</v>
+      </c>
+      <c r="G250" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H250" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I250" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="251" ht="18.0" hidden="1" customHeight="1">
+      <c r="A251" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="B251" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="C251" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D251" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E251" s="33">
+        <v>45.3378</v>
+      </c>
+      <c r="F251" s="33">
+        <v>14.405</v>
+      </c>
+      <c r="G251" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H251" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I251" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="252" ht="18.0" hidden="1" customHeight="1">
+      <c r="A252" s="32" t="s">
+        <v>545</v>
+      </c>
+      <c r="B252" s="32" t="s">
+        <v>546</v>
+      </c>
+      <c r="C252" s="32" t="s">
+        <v>547</v>
+      </c>
+      <c r="D252" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252" s="33">
+        <v>17.0658</v>
+      </c>
+      <c r="F252" s="33">
+        <v>54.0924</v>
+      </c>
+      <c r="G252" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H252" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I252" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="253" ht="18.0" hidden="1" customHeight="1">
+      <c r="A253" s="32" t="s">
+        <v>548</v>
+      </c>
+      <c r="B253" s="32" t="s">
+        <v>549</v>
+      </c>
+      <c r="C253" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="D253" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E253" s="33">
+        <v>24.9</v>
+      </c>
+      <c r="F253" s="33">
+        <v>51.55</v>
+      </c>
+      <c r="G253" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H253" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I253" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="254" ht="18.0" customHeight="1">
+      <c r="A254" s="32" t="s">
+        <v>550</v>
+      </c>
+      <c r="B254" s="32" t="s">
+        <v>551</v>
+      </c>
+      <c r="C254" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D254" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E254" s="33">
+        <v>32.9595</v>
+      </c>
+      <c r="F254" s="33">
+        <v>-117.2653</v>
+      </c>
+      <c r="G254" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H254" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I254" s="36" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="255" ht="18.0" hidden="1" customHeight="1">
+      <c r="A255" s="32" t="s">
+        <v>553</v>
+      </c>
+      <c r="B255" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="C255" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D255" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E255" s="33">
+        <v>30.3935</v>
+      </c>
+      <c r="F255" s="33">
+        <v>-86.3452</v>
+      </c>
+      <c r="G255" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H255" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I255" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="256" ht="18.0" hidden="1" customHeight="1">
+      <c r="A256" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="B256" s="32" t="s">
+        <v>555</v>
+      </c>
+      <c r="C256" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D256" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E256" s="33">
+        <v>28.9167</v>
+      </c>
+      <c r="F256" s="33">
+        <v>117.9833</v>
+      </c>
+      <c r="G256" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H256" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I256" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="257" ht="18.0" hidden="1" customHeight="1">
+      <c r="A257" s="32" t="s">
+        <v>556</v>
+      </c>
+      <c r="B257" s="32" t="s">
+        <v>557</v>
+      </c>
+      <c r="C257" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D257" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E257" s="33">
+        <v>34.414</v>
+      </c>
+      <c r="F257" s="33">
+        <v>-119.6982</v>
+      </c>
+      <c r="G257" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H257" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I257" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="258" ht="18.0" customHeight="1">
+      <c r="A258" s="32" t="s">
+        <v>558</v>
+      </c>
+      <c r="B258" s="32" t="s">
+        <v>559</v>
+      </c>
+      <c r="C258" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D258" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E258" s="33">
+        <v>35.7783</v>
+      </c>
+      <c r="F258" s="33">
+        <v>-106.0719</v>
+      </c>
+      <c r="G258" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H258" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I258" s="36" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="259" ht="18.0" customHeight="1">
+      <c r="A259" s="32" t="s">
+        <v>561</v>
+      </c>
+      <c r="B259" s="32" t="s">
+        <v>562</v>
+      </c>
+      <c r="C259" s="32" t="s">
         <v>417</v>
       </c>
-      <c r="B193" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C193" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D193" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E193" s="32">
-        <v>41.8508</v>
-      </c>
-      <c r="F193" s="32">
-        <v>-87.9401</v>
-      </c>
-      <c r="G193" s="31" t="s">
+      <c r="D259" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E259" s="33">
+        <v>11.2408</v>
+      </c>
+      <c r="F259" s="33">
+        <v>-74.199</v>
+      </c>
+      <c r="G259" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H193" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I193" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="194" ht="18.0" hidden="1" customHeight="1">
-      <c r="A194" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="B194" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="C194" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="D194" s="31" t="s">
+      <c r="H259" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I259" s="36" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="260" ht="18.0" hidden="1" customHeight="1">
+      <c r="A260" s="32" t="s">
+        <v>564</v>
+      </c>
+      <c r="B260" s="32" t="s">
+        <v>565</v>
+      </c>
+      <c r="C260" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D260" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E194" s="32">
-        <v>15.179</v>
-      </c>
-      <c r="F194" s="32">
-        <v>120.539</v>
-      </c>
-      <c r="G194" s="31" t="s">
+      <c r="E260" s="33">
+        <v>18.2206</v>
+      </c>
+      <c r="F260" s="33">
+        <v>109.5083</v>
+      </c>
+      <c r="G260" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H194" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I194" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="195" ht="18.0" hidden="1" customHeight="1">
-      <c r="A195" s="31" t="s">
-        <v>422</v>
-      </c>
-      <c r="B195" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C195" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D195" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E195" s="32">
-        <v>27.9768</v>
-      </c>
-      <c r="F195" s="32">
-        <v>-82.8272</v>
-      </c>
-      <c r="G195" s="31" t="s">
+      <c r="H260" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I260" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="261" ht="18.0" hidden="1" customHeight="1">
+      <c r="A261" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="B261" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C261" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D261" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E261" s="33">
+        <v>33.6589</v>
+      </c>
+      <c r="F261" s="33">
+        <v>-111.8743</v>
+      </c>
+      <c r="G261" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H195" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I195" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="196" ht="18.0" hidden="1" customHeight="1">
-      <c r="A196" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="B196" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="C196" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="D196" s="31" t="s">
+      <c r="H261" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I261" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="262" ht="18.0" hidden="1" customHeight="1">
+      <c r="A262" s="32" t="s">
+        <v>567</v>
+      </c>
+      <c r="B262" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="C262" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D262" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E262" s="33">
+        <v>34.8121</v>
+      </c>
+      <c r="F262" s="33">
+        <v>-111.7562</v>
+      </c>
+      <c r="G262" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H262" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I262" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="263" ht="18.0" hidden="1" customHeight="1">
+      <c r="A263" s="32" t="s">
+        <v>568</v>
+      </c>
+      <c r="B263" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C263" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="D263" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E263" s="33">
+        <v>-4.55</v>
+      </c>
+      <c r="F263" s="33">
+        <v>55.4333</v>
+      </c>
+      <c r="G263" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H263" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I263" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="264" ht="18.0" customHeight="1">
+      <c r="A264" s="32" t="s">
+        <v>569</v>
+      </c>
+      <c r="B264" s="32" t="s">
+        <v>570</v>
+      </c>
+      <c r="C264" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D264" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E196" s="32">
-        <v>36.7333</v>
-      </c>
-      <c r="F196" s="32">
-        <v>28.7667</v>
-      </c>
-      <c r="G196" s="31" t="s">
+      <c r="E264" s="33">
+        <v>40.6268</v>
+      </c>
+      <c r="F264" s="33">
+        <v>14.3747</v>
+      </c>
+      <c r="G264" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H196" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I196" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="197" ht="18.0" hidden="1" customHeight="1">
-      <c r="A197" s="31" t="s">
-        <v>425</v>
-      </c>
-      <c r="B197" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="C197" s="31" t="s">
+      <c r="H264" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I264" s="36" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="265" ht="18.0" hidden="1" customHeight="1">
+      <c r="A265" s="32" t="s">
+        <v>572</v>
+      </c>
+      <c r="B265" s="32" t="s">
+        <v>573</v>
+      </c>
+      <c r="C265" s="32" t="s">
+        <v>574</v>
+      </c>
+      <c r="D265" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E265" s="33">
+        <v>53.9</v>
+      </c>
+      <c r="F265" s="33">
+        <v>14.25</v>
+      </c>
+      <c r="G265" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H265" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I265" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="266" ht="18.0" hidden="1" customHeight="1">
+      <c r="A266" s="32" t="s">
+        <v>575</v>
+      </c>
+      <c r="B266" s="32" t="s">
+        <v>576</v>
+      </c>
+      <c r="C266" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D266" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E266" s="33">
+        <v>35.7673</v>
+      </c>
+      <c r="F266" s="33">
+        <v>-5.7998</v>
+      </c>
+      <c r="G266" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H266" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I266" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267" ht="18.0" hidden="1" customHeight="1">
+      <c r="A267" s="32" t="s">
+        <v>577</v>
+      </c>
+      <c r="B267" s="32" t="s">
+        <v>578</v>
+      </c>
+      <c r="C267" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D267" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E267" s="33">
+        <v>35.6329</v>
+      </c>
+      <c r="F267" s="33">
+        <v>139.871</v>
+      </c>
+      <c r="G267" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H267" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I267" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268" ht="18.0" hidden="1" customHeight="1">
+      <c r="A268" s="32" t="s">
+        <v>579</v>
+      </c>
+      <c r="B268" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C268" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D268" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E268" s="33">
+        <v>20.2114</v>
+      </c>
+      <c r="F268" s="33">
+        <v>-87.4654</v>
+      </c>
+      <c r="G268" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H268" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I268" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269" ht="18.0" hidden="1" customHeight="1">
+      <c r="A269" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="B269" s="32" t="s">
+        <v>581</v>
+      </c>
+      <c r="C269" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D269" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E269" s="33">
+        <v>20.6534</v>
+      </c>
+      <c r="F269" s="33">
+        <v>-105.2253</v>
+      </c>
+      <c r="G269" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H269" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I269" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270" ht="18.0" hidden="1" customHeight="1">
+      <c r="A270" s="32" t="s">
+        <v>582</v>
+      </c>
+      <c r="B270" s="32" t="s">
+        <v>583</v>
+      </c>
+      <c r="C270" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D270" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E270" s="33">
+        <v>37.0667</v>
+      </c>
+      <c r="F270" s="33">
+        <v>-8.1167</v>
+      </c>
+      <c r="G270" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H270" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I270" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="271" ht="18.0" hidden="1" customHeight="1">
+      <c r="A271" s="32" t="s">
+        <v>584</v>
+      </c>
+      <c r="B271" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C271" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D271" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E271" s="33">
+        <v>36.8529</v>
+      </c>
+      <c r="F271" s="33">
+        <v>-75.978</v>
+      </c>
+      <c r="G271" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H271" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I271" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="272" ht="18.0" hidden="1" customHeight="1">
+      <c r="A272" s="32" t="s">
+        <v>585</v>
+      </c>
+      <c r="B272" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="C272" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D272" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E272" s="33">
+        <v>21.2793</v>
+      </c>
+      <c r="F272" s="33">
+        <v>-157.831</v>
+      </c>
+      <c r="G272" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H272" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I272" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="273" ht="18.0" hidden="1" customHeight="1">
+      <c r="A273" s="32" t="s">
+        <v>586</v>
+      </c>
+      <c r="B273" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="C273" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D273" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E273" s="33">
+        <v>19.9261</v>
+      </c>
+      <c r="F273" s="33">
+        <v>-155.886</v>
+      </c>
+      <c r="G273" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H273" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I273" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="274" ht="18.0" hidden="1" customHeight="1">
+      <c r="A274" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="B274" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="C274" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D274" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E274" s="33">
+        <v>50.1163</v>
+      </c>
+      <c r="F274" s="33">
+        <v>-122.9574</v>
+      </c>
+      <c r="G274" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H274" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I274" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="275" ht="18.0" hidden="1" customHeight="1">
+      <c r="A275" s="32" t="s">
+        <v>588</v>
+      </c>
+      <c r="B275" s="32" t="s">
+        <v>589</v>
+      </c>
+      <c r="C275" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D275" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E275" s="33">
+        <v>6.3833</v>
+      </c>
+      <c r="F275" s="33">
+        <v>81.5167</v>
+      </c>
+      <c r="G275" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H275" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I275" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="276" ht="18.0" customHeight="1">
+      <c r="A276" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="B276" s="32" t="s">
+        <v>591</v>
+      </c>
+      <c r="C276" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D197" s="31" t="s">
+      <c r="D276" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E197" s="32">
-        <v>25.6941</v>
-      </c>
-      <c r="F197" s="32">
-        <v>100.16</v>
-      </c>
-      <c r="G197" s="31" t="s">
+      <c r="E276" s="33">
+        <v>24.35</v>
+      </c>
+      <c r="F276" s="33">
+        <v>102.9167</v>
+      </c>
+      <c r="G276" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H197" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I197" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="198" ht="18.0" hidden="1" customHeight="1">
-      <c r="A198" s="31" t="s">
-        <v>427</v>
-      </c>
-      <c r="B198" s="31" t="s">
-        <v>428</v>
-      </c>
-      <c r="C198" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D198" s="31" t="s">
+      <c r="H276" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I276" s="36" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="277" ht="18.0" hidden="1" customHeight="1">
+      <c r="A277" s="32" t="s">
+        <v>593</v>
+      </c>
+      <c r="B277" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C277" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D277" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E277" s="33">
+        <v>36.1299</v>
+      </c>
+      <c r="F277" s="33">
+        <v>-115.1658</v>
+      </c>
+      <c r="G277" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="H277" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I277" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="278" ht="18.0" customHeight="1">
+      <c r="A278" s="32" t="s">
+        <v>594</v>
+      </c>
+      <c r="B278" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="C278" s="32" t="s">
+        <v>596</v>
+      </c>
+      <c r="D278" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E198" s="32">
-        <v>38.914</v>
-      </c>
-      <c r="F198" s="32">
-        <v>121.6147</v>
-      </c>
-      <c r="G198" s="31" t="s">
+      <c r="E278" s="33">
+        <v>-28.0028</v>
+      </c>
+      <c r="F278" s="33">
+        <v>153.4307</v>
+      </c>
+      <c r="G278" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H198" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I198" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="199" ht="18.0" customHeight="1">
-      <c r="A199" s="31" t="s">
-        <v>429</v>
-      </c>
-      <c r="B199" s="31" t="s">
-        <v>430</v>
-      </c>
-      <c r="C199" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D199" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E199" s="32">
-        <v>32.93</v>
-      </c>
-      <c r="F199" s="32">
-        <v>-96.4597</v>
-      </c>
-      <c r="G199" s="31" t="s">
+      <c r="H278" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I278" s="36" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="279" ht="18.0" customHeight="1">
+      <c r="A279" s="32" t="s">
+        <v>598</v>
+      </c>
+      <c r="B279" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="C279" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="D279" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E279" s="33">
+        <v>18.4655</v>
+      </c>
+      <c r="F279" s="33">
+        <v>-66.1057</v>
+      </c>
+      <c r="G279" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H199" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I199" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="200" ht="18.0" hidden="1" customHeight="1">
-      <c r="A200" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="B200" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="C200" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D200" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E200" s="32">
-        <v>29.2108</v>
-      </c>
-      <c r="F200" s="32">
-        <v>-81.0228</v>
-      </c>
-      <c r="G200" s="31" t="s">
+      <c r="H279" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I279" s="36" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="280" ht="18.0" hidden="1" customHeight="1">
+      <c r="A280" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="B280" s="32" t="s">
+        <v>601</v>
+      </c>
+      <c r="C280" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D280" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E280" s="33">
+        <v>39.5997</v>
+      </c>
+      <c r="F280" s="33">
+        <v>-104.8761</v>
+      </c>
+      <c r="G280" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H200" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I200" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="201" ht="18.0" hidden="1" customHeight="1">
-      <c r="A201" s="31" t="s">
-        <v>432</v>
-      </c>
-      <c r="B201" s="31" t="s">
-        <v>433</v>
-      </c>
-      <c r="C201" s="31" t="s">
-        <v>434</v>
-      </c>
-      <c r="D201" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E201" s="32">
-        <v>31.7667</v>
-      </c>
-      <c r="F201" s="32">
-        <v>35.5833</v>
-      </c>
-      <c r="G201" s="31" t="s">
+      <c r="H280" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I280" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="281" ht="18.0" customHeight="1">
+      <c r="A281" s="32" t="s">
+        <v>602</v>
+      </c>
+      <c r="B281" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C281" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D281" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E281" s="33">
+        <v>30.246</v>
+      </c>
+      <c r="F281" s="33">
+        <v>-87.7009</v>
+      </c>
+      <c r="G281" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H201" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I201" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="202" ht="18.0" customHeight="1">
-      <c r="A202" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="B202" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="C202" s="31" t="s">
-        <v>437</v>
-      </c>
-      <c r="D202" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E202" s="32">
-        <v>25.2854</v>
-      </c>
-      <c r="F202" s="32">
-        <v>51.531</v>
-      </c>
-      <c r="G202" s="31" t="s">
+      <c r="H281" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I281" s="36" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="282" ht="18.0" hidden="1" customHeight="1">
+      <c r="A282" s="32" t="s">
+        <v>604</v>
+      </c>
+      <c r="B282" s="32" t="s">
+        <v>605</v>
+      </c>
+      <c r="C282" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D282" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E282" s="33">
+        <v>33.6595</v>
+      </c>
+      <c r="F282" s="33">
+        <v>-118.0077</v>
+      </c>
+      <c r="G282" s="32" t="s">
         <v>385</v>
       </c>
-      <c r="H202" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I202" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="203" ht="18.0" customHeight="1">
-      <c r="A203" s="31" t="s">
-        <v>438</v>
-      </c>
-      <c r="B203" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="C203" s="31" t="s">
-        <v>437</v>
-      </c>
-      <c r="D203" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E203" s="32">
-        <v>25.3725</v>
-      </c>
-      <c r="F203" s="32">
-        <v>51.5505</v>
-      </c>
-      <c r="G203" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H203" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I203" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="204" ht="18.0" hidden="1" customHeight="1">
-      <c r="A204" s="31" t="s">
-        <v>439</v>
-      </c>
-      <c r="B204" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C204" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D204" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E204" s="32">
-        <v>25.097</v>
-      </c>
-      <c r="F204" s="32">
-        <v>55.1447</v>
-      </c>
-      <c r="G204" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H204" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I204" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="205" ht="18.0" hidden="1" customHeight="1">
-      <c r="A205" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="B205" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C205" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D205" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E205" s="32">
-        <v>25.1124</v>
-      </c>
-      <c r="F205" s="32">
-        <v>55.139</v>
-      </c>
-      <c r="G205" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H205" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I205" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="206" ht="18.0" customHeight="1">
-      <c r="A206" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="B206" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C206" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="D206" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E206" s="32">
-        <v>25.0781</v>
-      </c>
-      <c r="F206" s="32">
-        <v>55.1305</v>
-      </c>
-      <c r="G206" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H206" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I206" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="207" ht="18.0" hidden="1" customHeight="1">
-      <c r="A207" s="31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B207" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="C207" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="D207" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E207" s="32">
-        <v>-17.7833</v>
-      </c>
-      <c r="F207" s="32">
-        <v>177.4167</v>
-      </c>
-      <c r="G207" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H207" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I207" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="208" ht="18.0" hidden="1" customHeight="1">
-      <c r="A208" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="B208" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C208" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D208" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E208" s="32">
-        <v>26.1224</v>
-      </c>
-      <c r="F208" s="32">
-        <v>-80.1034</v>
-      </c>
-      <c r="G208" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H208" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I208" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="209" ht="18.0" customHeight="1">
-      <c r="A209" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="B209" s="31" t="s">
-        <v>445</v>
-      </c>
-      <c r="C209" s="31" t="s">
-        <v>446</v>
-      </c>
-      <c r="D209" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E209" s="32">
-        <v>50.0259</v>
-      </c>
-      <c r="F209" s="32">
-        <v>8.835</v>
-      </c>
-      <c r="G209" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H209" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I209" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="210" ht="18.0" hidden="1" customHeight="1">
-      <c r="A210" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="B210" s="31" t="s">
-        <v>448</v>
-      </c>
-      <c r="C210" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D210" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E210" s="32">
-        <v>29.2108</v>
-      </c>
-      <c r="F210" s="32">
-        <v>-94.8639</v>
-      </c>
-      <c r="G210" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H210" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I210" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="211" ht="18.0" hidden="1" customHeight="1">
-      <c r="A211" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="B211" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C211" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="D211" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E211" s="32">
-        <v>15.4989</v>
-      </c>
-      <c r="F211" s="32">
-        <v>73.8278</v>
-      </c>
-      <c r="G211" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H211" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I211" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="212" ht="18.0" hidden="1" customHeight="1">
-      <c r="A212" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="B212" s="31" t="s">
-        <v>451</v>
-      </c>
-      <c r="C212" s="31" t="s">
-        <v>452</v>
-      </c>
-      <c r="D212" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E212" s="32">
-        <v>13.5135</v>
-      </c>
-      <c r="F212" s="32">
-        <v>144.7981</v>
-      </c>
-      <c r="G212" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H212" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I212" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="213" ht="18.0" customHeight="1">
-      <c r="A213" s="31" t="s">
-        <v>453</v>
-      </c>
-      <c r="B213" s="31" t="s">
-        <v>454</v>
-      </c>
-      <c r="C213" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="D213" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E213" s="32">
-        <v>35.8562</v>
-      </c>
-      <c r="F213" s="32">
-        <v>129.225</v>
-      </c>
-      <c r="G213" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H213" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I213" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="214" ht="18.0" hidden="1" customHeight="1">
-      <c r="A214" s="31" t="s">
-        <v>456</v>
-      </c>
-      <c r="B214" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C214" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D214" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E214" s="32">
-        <v>29.606</v>
-      </c>
-      <c r="F214" s="32">
-        <v>118.996</v>
-      </c>
-      <c r="G214" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H214" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I214" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="215" ht="18.0" hidden="1" customHeight="1">
-      <c r="A215" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="B215" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C215" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D215" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E215" s="32">
-        <v>21.2793</v>
-      </c>
-      <c r="F215" s="32">
-        <v>-157.8389</v>
-      </c>
-      <c r="G215" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H215" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I215" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="216" ht="18.0" customHeight="1">
-      <c r="A216" s="31" t="s">
-        <v>458</v>
-      </c>
-      <c r="B216" s="31" t="s">
-        <v>459</v>
-      </c>
-      <c r="C216" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D216" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E216" s="32">
-        <v>-17.5334</v>
-      </c>
-      <c r="F216" s="32">
-        <v>-149.5693</v>
-      </c>
-      <c r="G216" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H216" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I216" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="217" ht="18.0" hidden="1" customHeight="1">
-      <c r="A217" s="31" t="s">
-        <v>460</v>
-      </c>
-      <c r="B217" s="31" t="s">
-        <v>461</v>
-      </c>
-      <c r="C217" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D217" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E217" s="32">
-        <v>12.5667</v>
-      </c>
-      <c r="F217" s="32">
-        <v>99.9667</v>
-      </c>
-      <c r="G217" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H217" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I217" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="218" ht="18.0" hidden="1" customHeight="1">
-      <c r="A218" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="B218" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="C218" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D218" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E218" s="32">
-        <v>23.8833</v>
-      </c>
-      <c r="F218" s="32">
-        <v>114.4167</v>
-      </c>
-      <c r="G218" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H218" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I218" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="219" ht="18.0" customHeight="1">
-      <c r="A219" s="31" t="s">
-        <v>464</v>
-      </c>
-      <c r="B219" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="C219" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D219" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E219" s="32">
-        <v>27.2579</v>
-      </c>
-      <c r="F219" s="32">
-        <v>33.8116</v>
-      </c>
-      <c r="G219" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H219" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I219" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="220" ht="18.0" customHeight="1">
-      <c r="A220" s="31" t="s">
-        <v>466</v>
-      </c>
-      <c r="B220" s="31" t="s">
-        <v>467</v>
-      </c>
-      <c r="C220" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D220" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E220" s="32">
-        <v>32.905</v>
-      </c>
-      <c r="F220" s="32">
-        <v>-117.234</v>
-      </c>
-      <c r="G220" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H220" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I220" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="221" ht="18.0" hidden="1" customHeight="1">
-      <c r="A221" s="31" t="s">
-        <v>468</v>
-      </c>
-      <c r="B221" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="C221" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D221" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E221" s="32">
-        <v>36.0553</v>
-      </c>
-      <c r="F221" s="32">
-        <v>-114.9418</v>
-      </c>
-      <c r="G221" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H221" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I221" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="222" ht="18.0" hidden="1" customHeight="1">
-      <c r="A222" s="31" t="s">
-        <v>470</v>
-      </c>
-      <c r="B222" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="C222" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D222" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E222" s="32">
-        <v>22.8906</v>
-      </c>
-      <c r="F222" s="32">
-        <v>-109.9167</v>
-      </c>
-      <c r="G222" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H222" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I222" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="223" ht="18.0" hidden="1" customHeight="1">
-      <c r="A223" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="B223" s="31" t="s">
-        <v>472</v>
-      </c>
-      <c r="C223" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D223" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E223" s="32">
-        <v>25.6872</v>
-      </c>
-      <c r="F223" s="32">
-        <v>32.6396</v>
-      </c>
-      <c r="G223" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H223" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I223" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="224" ht="18.0" hidden="1" customHeight="1">
-      <c r="A224" s="31" t="s">
-        <v>473</v>
-      </c>
-      <c r="B224" s="31" t="s">
-        <v>474</v>
-      </c>
-      <c r="C224" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="D224" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E224" s="32">
-        <v>4.25</v>
-      </c>
-      <c r="F224" s="32">
-        <v>73.5833</v>
-      </c>
-      <c r="G224" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H224" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I224" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="225" ht="18.0" customHeight="1">
-      <c r="A225" s="31" t="s">
-        <v>475</v>
-      </c>
-      <c r="B225" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="C225" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D225" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E225" s="32">
-        <v>39.55</v>
-      </c>
-      <c r="F225" s="32">
-        <v>2.65</v>
-      </c>
-      <c r="G225" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H225" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I225" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="226" ht="18.0" customHeight="1">
-      <c r="A226" s="31" t="s">
-        <v>477</v>
-      </c>
-      <c r="B226" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C226" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="D226" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E226" s="32">
-        <v>35.9167</v>
-      </c>
-      <c r="F226" s="32">
-        <v>14.4833</v>
-      </c>
-      <c r="G226" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H226" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I226" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="227" ht="18.0" hidden="1" customHeight="1">
-      <c r="A227" s="31" t="s">
-        <v>478</v>
-      </c>
-      <c r="B227" s="31" t="s">
-        <v>479</v>
-      </c>
-      <c r="C227" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D227" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E227" s="32">
-        <v>25.9423</v>
-      </c>
-      <c r="F227" s="32">
-        <v>-81.7201</v>
-      </c>
-      <c r="G227" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H227" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I227" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="228" ht="18.0" hidden="1" customHeight="1">
-      <c r="A228" s="31" t="s">
-        <v>480</v>
-      </c>
-      <c r="B228" s="31" t="s">
-        <v>481</v>
-      </c>
-      <c r="C228" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D228" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E228" s="32">
-        <v>25.0667</v>
-      </c>
-      <c r="F228" s="32">
-        <v>34.8833</v>
-      </c>
-      <c r="G228" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H228" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I228" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="229" ht="18.0" hidden="1" customHeight="1">
-      <c r="A229" s="31" t="s">
-        <v>482</v>
-      </c>
-      <c r="B229" s="31" t="s">
-        <v>483</v>
-      </c>
-      <c r="C229" s="31" t="s">
-        <v>484</v>
-      </c>
-      <c r="D229" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="E229" s="32">
-        <v>-20.2833</v>
-      </c>
-      <c r="F229" s="32">
-        <v>57.3667</v>
-      </c>
-      <c r="G229" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H229" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I229" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="230" ht="18.0" hidden="1" customHeight="1">
-      <c r="A230" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="B230" s="31" t="s">
-        <v>486</v>
-      </c>
-      <c r="C230" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D230" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E230" s="32">
-        <v>-17.5</v>
-      </c>
-      <c r="F230" s="32">
-        <v>-149.8333</v>
-      </c>
-      <c r="G230" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H230" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I230" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="231" ht="18.0" hidden="1" customHeight="1">
-      <c r="A231" s="31" t="s">
-        <v>487</v>
-      </c>
-      <c r="B231" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C231" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D231" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E231" s="32">
-        <v>33.7041</v>
-      </c>
-      <c r="F231" s="32">
-        <v>-78.8764</v>
-      </c>
-      <c r="G231" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H231" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I231" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="232" ht="18.0" customHeight="1">
-      <c r="A232" s="31" t="s">
-        <v>488</v>
-      </c>
-      <c r="B232" s="31" t="s">
-        <v>489</v>
-      </c>
-      <c r="C232" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D232" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E232" s="32">
-        <v>31.67</v>
-      </c>
-      <c r="F232" s="32">
-        <v>118.83</v>
-      </c>
-      <c r="G232" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H232" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I232" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="233" ht="18.0" customHeight="1">
-      <c r="A233" s="31" t="s">
-        <v>490</v>
-      </c>
-      <c r="B233" s="31" t="s">
-        <v>491</v>
-      </c>
-      <c r="C233" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D233" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E233" s="32">
-        <v>29.8047</v>
-      </c>
-      <c r="F233" s="32">
-        <v>121.5654</v>
-      </c>
-      <c r="G233" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H233" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I233" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="234" ht="18.0" hidden="1" customHeight="1">
-      <c r="A234" s="31" t="s">
-        <v>492</v>
-      </c>
-      <c r="B234" s="31" t="s">
-        <v>493</v>
-      </c>
-      <c r="C234" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D234" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E234" s="32">
-        <v>42.7896</v>
-      </c>
-      <c r="F234" s="32">
-        <v>140.6864</v>
-      </c>
-      <c r="G234" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H234" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I234" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="235" ht="18.0" customHeight="1">
-      <c r="A235" s="31" t="s">
-        <v>494</v>
-      </c>
-      <c r="B235" s="31" t="s">
-        <v>495</v>
-      </c>
-      <c r="C235" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D235" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E235" s="32">
-        <v>38.3365</v>
-      </c>
-      <c r="F235" s="32">
-        <v>-75.0849</v>
-      </c>
-      <c r="G235" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H235" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I235" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="236" ht="18.0" hidden="1" customHeight="1">
-      <c r="A236" s="31" t="s">
-        <v>496</v>
-      </c>
-      <c r="B236" s="31" t="s">
-        <v>497</v>
-      </c>
-      <c r="C236" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D236" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E236" s="32">
-        <v>35.2553</v>
-      </c>
-      <c r="F236" s="32">
-        <v>139.15</v>
-      </c>
-      <c r="G236" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H236" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I236" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="237" ht="18.0" hidden="1" customHeight="1">
-      <c r="A237" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="B237" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C237" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D237" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E237" s="32">
-        <v>26.3167</v>
-      </c>
-      <c r="F237" s="32">
-        <v>127.75</v>
-      </c>
-      <c r="G237" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H237" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I237" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="238" ht="18.0" hidden="1" customHeight="1">
-      <c r="A238" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="B238" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="C238" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D238" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E238" s="32">
-        <v>24.8056</v>
-      </c>
-      <c r="F238" s="32">
-        <v>125.2814</v>
-      </c>
-      <c r="G238" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H238" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I238" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="239" ht="18.0" hidden="1" customHeight="1">
-      <c r="A239" s="31" t="s">
-        <v>501</v>
-      </c>
-      <c r="B239" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="C239" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D239" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E239" s="32">
-        <v>26.6333</v>
-      </c>
-      <c r="F239" s="32">
-        <v>127.8667</v>
-      </c>
-      <c r="G239" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H239" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I239" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="240" ht="18.0" customHeight="1">
-      <c r="A240" s="31" t="s">
-        <v>503</v>
-      </c>
-      <c r="B240" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C240" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D240" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E240" s="32">
-        <v>28.4177</v>
-      </c>
-      <c r="F240" s="32">
-        <v>-81.5812</v>
-      </c>
-      <c r="G240" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H240" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I240" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="241" ht="18.0" customHeight="1">
-      <c r="A241" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="B241" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C241" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D241" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E241" s="32">
-        <v>28.3694</v>
-      </c>
-      <c r="F241" s="32">
-        <v>-81.516</v>
-      </c>
-      <c r="G241" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H241" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I241" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="242" ht="18.0" customHeight="1">
-      <c r="A242" s="31" t="s">
-        <v>505</v>
-      </c>
-      <c r="B242" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C242" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D242" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E242" s="32">
-        <v>28.3694</v>
-      </c>
-      <c r="F242" s="32">
-        <v>-81.516</v>
-      </c>
-      <c r="G242" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H242" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I242" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="243" ht="18.0" customHeight="1">
-      <c r="A243" s="31" t="s">
-        <v>506</v>
-      </c>
-      <c r="B243" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="C243" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D243" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E243" s="32">
-        <v>33.8303</v>
-      </c>
-      <c r="F243" s="32">
-        <v>-116.5453</v>
-      </c>
-      <c r="G243" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H243" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I243" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="244" ht="18.0" customHeight="1">
-      <c r="A244" s="31" t="s">
-        <v>507</v>
-      </c>
-      <c r="B244" s="31" t="s">
-        <v>508</v>
-      </c>
-      <c r="C244" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D244" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E244" s="32">
-        <v>12.9236</v>
-      </c>
-      <c r="F244" s="32">
-        <v>100.8825</v>
-      </c>
-      <c r="G244" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H244" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I244" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="245" ht="18.0" hidden="1" customHeight="1">
-      <c r="A245" s="31" t="s">
-        <v>509</v>
-      </c>
-      <c r="B245" s="31" t="s">
-        <v>510</v>
-      </c>
-      <c r="C245" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D245" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E245" s="32">
-        <v>30.3344</v>
-      </c>
-      <c r="F245" s="32">
-        <v>-87.1627</v>
-      </c>
-      <c r="G245" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H245" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I245" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="246" ht="18.0" hidden="1" customHeight="1">
-      <c r="A246" s="31" t="s">
-        <v>511</v>
-      </c>
-      <c r="B246" s="31" t="s">
-        <v>512</v>
-      </c>
-      <c r="C246" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D246" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E246" s="32">
-        <v>33.6589</v>
-      </c>
-      <c r="F246" s="32">
-        <v>-111.8743</v>
-      </c>
-      <c r="G246" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H246" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I246" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="247" ht="18.0" hidden="1" customHeight="1">
-      <c r="A247" s="31" t="s">
-        <v>513</v>
-      </c>
-      <c r="B247" s="31" t="s">
-        <v>512</v>
-      </c>
-      <c r="C247" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D247" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E247" s="32">
-        <v>33.6589</v>
-      </c>
-      <c r="F247" s="32">
-        <v>-111.8743</v>
-      </c>
-      <c r="G247" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H247" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I247" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="248" ht="18.0" hidden="1" customHeight="1">
-      <c r="A248" s="31" t="s">
-        <v>514</v>
-      </c>
-      <c r="B248" s="31" t="s">
-        <v>515</v>
-      </c>
-      <c r="C248" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="D248" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E248" s="32">
-        <v>17.9995</v>
-      </c>
-      <c r="F248" s="32">
-        <v>-66.6141</v>
-      </c>
-      <c r="G248" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H248" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I248" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="249" ht="18.0" customHeight="1">
-      <c r="A249" s="31" t="s">
-        <v>516</v>
-      </c>
-      <c r="B249" s="31" t="s">
-        <v>517</v>
-      </c>
-      <c r="C249" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="D249" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E249" s="32">
-        <v>29.9792</v>
-      </c>
-      <c r="F249" s="32">
-        <v>31.1342</v>
-      </c>
-      <c r="G249" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H249" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I249" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="250" ht="18.0" hidden="1" customHeight="1">
-      <c r="A250" s="31" t="s">
-        <v>518</v>
-      </c>
-      <c r="B250" s="31" t="s">
-        <v>519</v>
-      </c>
-      <c r="C250" s="31" t="s">
-        <v>520</v>
-      </c>
-      <c r="D250" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E250" s="32">
-        <v>-45.0312</v>
-      </c>
-      <c r="F250" s="32">
-        <v>168.6626</v>
-      </c>
-      <c r="G250" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H250" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I250" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="251" ht="18.0" hidden="1" customHeight="1">
-      <c r="A251" s="31" t="s">
-        <v>521</v>
-      </c>
-      <c r="B251" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="C251" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D251" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E251" s="32">
-        <v>45.3378</v>
-      </c>
-      <c r="F251" s="32">
-        <v>14.405</v>
-      </c>
-      <c r="G251" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H251" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I251" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="252" ht="18.0" hidden="1" customHeight="1">
-      <c r="A252" s="31" t="s">
-        <v>523</v>
-      </c>
-      <c r="B252" s="31" t="s">
-        <v>524</v>
-      </c>
-      <c r="C252" s="31" t="s">
-        <v>525</v>
-      </c>
-      <c r="D252" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E252" s="32">
-        <v>17.0658</v>
-      </c>
-      <c r="F252" s="32">
-        <v>54.0924</v>
-      </c>
-      <c r="G252" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H252" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I252" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="253" ht="18.0" hidden="1" customHeight="1">
-      <c r="A253" s="31" t="s">
-        <v>526</v>
-      </c>
-      <c r="B253" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="C253" s="31" t="s">
-        <v>437</v>
-      </c>
-      <c r="D253" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E253" s="32">
-        <v>24.9</v>
-      </c>
-      <c r="F253" s="32">
-        <v>51.55</v>
-      </c>
-      <c r="G253" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H253" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I253" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="254" ht="18.0" customHeight="1">
-      <c r="A254" s="31" t="s">
-        <v>528</v>
-      </c>
-      <c r="B254" s="31" t="s">
-        <v>529</v>
-      </c>
-      <c r="C254" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D254" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E254" s="32">
-        <v>32.9595</v>
-      </c>
-      <c r="F254" s="32">
-        <v>-117.2653</v>
-      </c>
-      <c r="G254" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H254" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I254" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="255" ht="18.0" hidden="1" customHeight="1">
-      <c r="A255" s="31" t="s">
-        <v>530</v>
-      </c>
-      <c r="B255" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C255" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D255" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E255" s="32">
-        <v>30.3935</v>
-      </c>
-      <c r="F255" s="32">
-        <v>-86.3452</v>
-      </c>
-      <c r="G255" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H255" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I255" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="256" ht="18.0" hidden="1" customHeight="1">
-      <c r="A256" s="31" t="s">
-        <v>531</v>
-      </c>
-      <c r="B256" s="31" t="s">
-        <v>532</v>
-      </c>
-      <c r="C256" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D256" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E256" s="32">
-        <v>28.9167</v>
-      </c>
-      <c r="F256" s="32">
-        <v>117.9833</v>
-      </c>
-      <c r="G256" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H256" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I256" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="257" ht="18.0" hidden="1" customHeight="1">
-      <c r="A257" s="31" t="s">
-        <v>533</v>
-      </c>
-      <c r="B257" s="31" t="s">
-        <v>534</v>
-      </c>
-      <c r="C257" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D257" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E257" s="32">
-        <v>34.414</v>
-      </c>
-      <c r="F257" s="32">
-        <v>-119.6982</v>
-      </c>
-      <c r="G257" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H257" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I257" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="258" ht="18.0" customHeight="1">
-      <c r="A258" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="B258" s="31" t="s">
-        <v>536</v>
-      </c>
-      <c r="C258" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D258" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E258" s="32">
-        <v>35.7783</v>
-      </c>
-      <c r="F258" s="32">
-        <v>-106.0719</v>
-      </c>
-      <c r="G258" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H258" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I258" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="259" ht="18.0" customHeight="1">
-      <c r="A259" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="B259" s="31" t="s">
-        <v>538</v>
-      </c>
-      <c r="C259" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="D259" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E259" s="32">
-        <v>11.2408</v>
-      </c>
-      <c r="F259" s="32">
-        <v>-74.199</v>
-      </c>
-      <c r="G259" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H259" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I259" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="260" ht="18.0" hidden="1" customHeight="1">
-      <c r="A260" s="31" t="s">
-        <v>539</v>
-      </c>
-      <c r="B260" s="31" t="s">
-        <v>540</v>
-      </c>
-      <c r="C260" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D260" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E260" s="32">
-        <v>18.2206</v>
-      </c>
-      <c r="F260" s="32">
-        <v>109.5083</v>
-      </c>
-      <c r="G260" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H260" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I260" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="261" ht="18.0" hidden="1" customHeight="1">
-      <c r="A261" s="31" t="s">
-        <v>541</v>
-      </c>
-      <c r="B261" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C261" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D261" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E261" s="32">
-        <v>33.6589</v>
-      </c>
-      <c r="F261" s="32">
-        <v>-111.8743</v>
-      </c>
-      <c r="G261" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H261" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I261" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="262" ht="18.0" hidden="1" customHeight="1">
-      <c r="A262" s="31" t="s">
-        <v>542</v>
-      </c>
-      <c r="B262" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="C262" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D262" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E262" s="32">
-        <v>34.8121</v>
-      </c>
-      <c r="F262" s="32">
-        <v>-111.7562</v>
-      </c>
-      <c r="G262" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H262" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I262" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="263" ht="18.0" hidden="1" customHeight="1">
-      <c r="A263" s="31" t="s">
-        <v>543</v>
-      </c>
-      <c r="B263" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="C263" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D263" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="E263" s="32">
-        <v>-4.55</v>
-      </c>
-      <c r="F263" s="32">
-        <v>55.4333</v>
-      </c>
-      <c r="G263" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H263" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I263" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="264" ht="18.0" customHeight="1">
-      <c r="A264" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="B264" s="31" t="s">
-        <v>545</v>
-      </c>
-      <c r="C264" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D264" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E264" s="32">
-        <v>40.6268</v>
-      </c>
-      <c r="F264" s="32">
-        <v>14.3747</v>
-      </c>
-      <c r="G264" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H264" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I264" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="265" ht="18.0" hidden="1" customHeight="1">
-      <c r="A265" s="31" t="s">
-        <v>546</v>
-      </c>
-      <c r="B265" s="31" t="s">
-        <v>547</v>
-      </c>
-      <c r="C265" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="D265" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E265" s="32">
-        <v>53.9</v>
-      </c>
-      <c r="F265" s="32">
-        <v>14.25</v>
-      </c>
-      <c r="G265" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H265" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I265" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="266" ht="18.0" hidden="1" customHeight="1">
-      <c r="A266" s="31" t="s">
-        <v>549</v>
-      </c>
-      <c r="B266" s="31" t="s">
-        <v>550</v>
-      </c>
-      <c r="C266" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="D266" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="E266" s="32">
-        <v>35.7673</v>
-      </c>
-      <c r="F266" s="32">
-        <v>-5.7998</v>
-      </c>
-      <c r="G266" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H266" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I266" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="267" ht="18.0" hidden="1" customHeight="1">
-      <c r="A267" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="B267" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="C267" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="D267" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E267" s="32">
-        <v>35.6329</v>
-      </c>
-      <c r="F267" s="32">
-        <v>139.871</v>
-      </c>
-      <c r="G267" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H267" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I267" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="268" ht="18.0" hidden="1" customHeight="1">
-      <c r="A268" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B268" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C268" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D268" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E268" s="32">
-        <v>20.2114</v>
-      </c>
-      <c r="F268" s="32">
-        <v>-87.4654</v>
-      </c>
-      <c r="G268" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H268" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I268" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="269" ht="18.0" hidden="1" customHeight="1">
-      <c r="A269" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="B269" s="31" t="s">
-        <v>555</v>
-      </c>
-      <c r="C269" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D269" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E269" s="32">
-        <v>20.6534</v>
-      </c>
-      <c r="F269" s="32">
-        <v>-105.2253</v>
-      </c>
-      <c r="G269" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H269" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I269" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="270" ht="18.0" hidden="1" customHeight="1">
-      <c r="A270" s="31" t="s">
-        <v>556</v>
-      </c>
-      <c r="B270" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="C270" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D270" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E270" s="32">
-        <v>37.0667</v>
-      </c>
-      <c r="F270" s="32">
-        <v>-8.1167</v>
-      </c>
-      <c r="G270" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H270" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I270" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="271" ht="18.0" hidden="1" customHeight="1">
-      <c r="A271" s="31" t="s">
-        <v>558</v>
-      </c>
-      <c r="B271" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C271" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D271" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E271" s="32">
-        <v>36.8529</v>
-      </c>
-      <c r="F271" s="32">
-        <v>-75.978</v>
-      </c>
-      <c r="G271" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H271" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I271" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="272" ht="18.0" hidden="1" customHeight="1">
-      <c r="A272" s="31" t="s">
-        <v>559</v>
-      </c>
-      <c r="B272" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C272" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D272" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E272" s="32">
-        <v>21.2793</v>
-      </c>
-      <c r="F272" s="32">
-        <v>-157.831</v>
-      </c>
-      <c r="G272" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H272" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I272" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="273" ht="18.0" hidden="1" customHeight="1">
-      <c r="A273" s="31" t="s">
-        <v>560</v>
-      </c>
-      <c r="B273" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="C273" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D273" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E273" s="32">
-        <v>19.9261</v>
-      </c>
-      <c r="F273" s="32">
-        <v>-155.886</v>
-      </c>
-      <c r="G273" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H273" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I273" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="274" ht="18.0" hidden="1" customHeight="1">
-      <c r="A274" s="31" t="s">
-        <v>561</v>
-      </c>
-      <c r="B274" s="31" t="s">
-        <v>331</v>
-      </c>
-      <c r="C274" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="D274" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E274" s="32">
-        <v>50.1163</v>
-      </c>
-      <c r="F274" s="32">
-        <v>-122.9574</v>
-      </c>
-      <c r="G274" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H274" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I274" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="275" ht="18.0" hidden="1" customHeight="1">
-      <c r="A275" s="31" t="s">
-        <v>562</v>
-      </c>
-      <c r="B275" s="31" t="s">
-        <v>563</v>
-      </c>
-      <c r="C275" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="D275" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E275" s="32">
-        <v>6.3833</v>
-      </c>
-      <c r="F275" s="32">
-        <v>81.5167</v>
-      </c>
-      <c r="G275" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H275" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I275" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="276" ht="18.0" customHeight="1">
-      <c r="A276" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="B276" s="31" t="s">
-        <v>565</v>
-      </c>
-      <c r="C276" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D276" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E276" s="32">
-        <v>24.35</v>
-      </c>
-      <c r="F276" s="32">
-        <v>102.9167</v>
-      </c>
-      <c r="G276" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H276" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I276" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="277" ht="18.0" hidden="1" customHeight="1">
-      <c r="A277" s="31" t="s">
-        <v>566</v>
-      </c>
-      <c r="B277" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C277" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D277" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E277" s="32">
-        <v>36.1299</v>
-      </c>
-      <c r="F277" s="32">
-        <v>-115.1658</v>
-      </c>
-      <c r="G277" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H277" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I277" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="278" ht="18.0" customHeight="1">
-      <c r="A278" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="B278" s="31" t="s">
-        <v>568</v>
-      </c>
-      <c r="C278" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="D278" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E278" s="32">
-        <v>-28.0028</v>
-      </c>
-      <c r="F278" s="32">
-        <v>153.4307</v>
-      </c>
-      <c r="G278" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H278" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I278" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="279" ht="18.0" customHeight="1">
-      <c r="A279" s="31" t="s">
-        <v>570</v>
-      </c>
-      <c r="B279" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="C279" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="D279" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E279" s="32">
-        <v>18.4655</v>
-      </c>
-      <c r="F279" s="32">
-        <v>-66.1057</v>
-      </c>
-      <c r="G279" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H279" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I279" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="280" ht="18.0" hidden="1" customHeight="1">
-      <c r="A280" s="31" t="s">
-        <v>571</v>
-      </c>
-      <c r="B280" s="31" t="s">
-        <v>572</v>
-      </c>
-      <c r="C280" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D280" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E280" s="32">
-        <v>39.5997</v>
-      </c>
-      <c r="F280" s="32">
-        <v>-104.8761</v>
-      </c>
-      <c r="G280" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H280" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I280" s="34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="281" ht="18.0" customHeight="1">
-      <c r="A281" s="31" t="s">
-        <v>573</v>
-      </c>
-      <c r="B281" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="C281" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D281" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E281" s="32">
-        <v>30.246</v>
-      </c>
-      <c r="F281" s="32">
-        <v>-87.7009</v>
-      </c>
-      <c r="G281" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H281" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I281" s="36" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="282" ht="18.0" hidden="1" customHeight="1">
-      <c r="A282" s="31" t="s">
-        <v>574</v>
-      </c>
-      <c r="B282" s="31" t="s">
-        <v>575</v>
-      </c>
-      <c r="C282" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D282" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E282" s="32">
-        <v>33.6595</v>
-      </c>
-      <c r="F282" s="32">
-        <v>-118.0077</v>
-      </c>
-      <c r="G282" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="H282" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I282" s="34" t="s">
+      <c r="H282" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I282" s="35" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="283" ht="18.0" hidden="1" customHeight="1">
       <c r="A283" s="37" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="B283" s="37" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="C283" s="37" t="s">
         <v>208</v>
@@ -10842,7 +10972,7 @@
         <v>-74.6</v>
       </c>
       <c r="G283" s="37" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="H283" s="39" t="s">
         <v>7</v>
@@ -10853,10 +10983,10 @@
     </row>
     <row r="284" ht="18.0" customHeight="1">
       <c r="A284" s="41" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="B284" s="41" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="C284" s="41" t="s">
         <v>31</v>
@@ -10871,18 +11001,18 @@
         <v>-112.0261</v>
       </c>
       <c r="G284" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H284" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I284" s="44" t="s">
-        <v>397</v>
+        <v>611</v>
       </c>
     </row>
     <row r="285" ht="18.0" hidden="1" customHeight="1">
       <c r="A285" s="41" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="B285" s="41" t="s">
         <v>97</v>
@@ -10900,7 +11030,7 @@
         <v>-117.1795</v>
       </c>
       <c r="G285" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H285" s="43" t="s">
         <v>7</v>
@@ -10911,7 +11041,7 @@
     </row>
     <row r="286" ht="18.0" hidden="1" customHeight="1">
       <c r="A286" s="41" t="s">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="B286" s="41" t="s">
         <v>42</v>
@@ -10929,7 +11059,7 @@
         <v>-115.1658</v>
       </c>
       <c r="G286" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H286" s="43" t="s">
         <v>7</v>
@@ -10940,7 +11070,7 @@
     </row>
     <row r="287" ht="18.0" hidden="1" customHeight="1">
       <c r="A287" s="41" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="B287" s="41" t="s">
         <v>164</v>
@@ -10958,7 +11088,7 @@
         <v>-157.831</v>
       </c>
       <c r="G287" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H287" s="43" t="s">
         <v>7</v>
@@ -10969,13 +11099,13 @@
     </row>
     <row r="288" ht="18.0" customHeight="1">
       <c r="A288" s="41" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="B288" s="41" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C288" s="41" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D288" s="41" t="s">
         <v>12</v>
@@ -10987,18 +11117,18 @@
         <v>51.5505</v>
       </c>
       <c r="G288" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H288" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I288" s="44" t="s">
-        <v>397</v>
+        <v>616</v>
       </c>
     </row>
     <row r="289" ht="18.0" customHeight="1">
       <c r="A289" s="41" t="s">
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="B289" s="41" t="s">
         <v>215</v>
@@ -11016,24 +11146,24 @@
         <v>55.5167</v>
       </c>
       <c r="G289" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H289" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I289" s="44" t="s">
-        <v>397</v>
+        <v>618</v>
       </c>
     </row>
     <row r="290" ht="18.0" customHeight="1">
       <c r="A290" s="41" t="s">
-        <v>586</v>
+        <v>619</v>
       </c>
       <c r="B290" s="41" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C290" s="41" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D290" s="41" t="s">
         <v>12</v>
@@ -11045,21 +11175,21 @@
         <v>51.531</v>
       </c>
       <c r="G290" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H290" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I290" s="44" t="s">
-        <v>397</v>
+        <v>620</v>
       </c>
     </row>
     <row r="291" ht="18.0" customHeight="1">
       <c r="A291" s="41" t="s">
-        <v>587</v>
+        <v>621</v>
       </c>
       <c r="B291" s="41" t="s">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="C291" s="41" t="s">
         <v>200</v>
@@ -11074,18 +11204,18 @@
         <v>135.7681</v>
       </c>
       <c r="G291" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H291" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I291" s="44" t="s">
-        <v>397</v>
+        <v>623</v>
       </c>
     </row>
     <row r="292" ht="18.0" customHeight="1">
       <c r="A292" s="41" t="s">
-        <v>589</v>
+        <v>624</v>
       </c>
       <c r="B292" s="41" t="s">
         <v>97</v>
@@ -11103,18 +11233,18 @@
         <v>-117.1795</v>
       </c>
       <c r="G292" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H292" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I292" s="44" t="s">
-        <v>397</v>
+        <v>625</v>
       </c>
     </row>
     <row r="293" ht="18.0" customHeight="1">
       <c r="A293" s="41" t="s">
-        <v>590</v>
+        <v>626</v>
       </c>
       <c r="B293" s="41" t="s">
         <v>169</v>
@@ -11132,18 +11262,18 @@
         <v>27.4305</v>
       </c>
       <c r="G293" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H293" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I293" s="44" t="s">
-        <v>397</v>
+        <v>627</v>
       </c>
     </row>
     <row r="294" ht="18.0" customHeight="1">
       <c r="A294" s="41" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="B294" s="41" t="s">
         <v>20</v>
@@ -11161,24 +11291,24 @@
         <v>115.212</v>
       </c>
       <c r="G294" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H294" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I294" s="44" t="s">
-        <v>397</v>
+        <v>629</v>
       </c>
     </row>
     <row r="295" ht="18.0" hidden="1" customHeight="1">
       <c r="A295" s="41" t="s">
-        <v>592</v>
+        <v>630</v>
       </c>
       <c r="B295" s="41" t="s">
-        <v>593</v>
+        <v>631</v>
       </c>
       <c r="C295" s="41" t="s">
-        <v>593</v>
+        <v>631</v>
       </c>
       <c r="D295" s="41" t="s">
         <v>32</v>
@@ -11190,7 +11320,7 @@
         <v>-63.0697</v>
       </c>
       <c r="G295" s="41" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="H295" s="43" t="s">
         <v>7</v>
@@ -11201,10 +11331,10 @@
     </row>
     <row r="296" ht="18.0" hidden="1" customHeight="1">
       <c r="A296" s="46" t="s">
-        <v>594</v>
+        <v>632</v>
       </c>
       <c r="B296" s="46" t="s">
-        <v>595</v>
+        <v>633</v>
       </c>
       <c r="C296" s="46" t="s">
         <v>31</v>
@@ -11219,7 +11349,7 @@
         <v>-98.6095</v>
       </c>
       <c r="G296" s="46" t="s">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="H296" s="48" t="s">
         <v>7</v>
@@ -11230,7 +11360,7 @@
     </row>
     <row r="297" ht="18.0" customHeight="1">
       <c r="A297" s="46" t="s">
-        <v>597</v>
+        <v>635</v>
       </c>
       <c r="B297" s="46" t="s">
         <v>47</v>
@@ -11248,24 +11378,24 @@
         <v>-81.516</v>
       </c>
       <c r="G297" s="46" t="s">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="H297" s="48" t="s">
         <v>7</v>
       </c>
       <c r="I297" s="50" t="s">
-        <v>397</v>
+        <v>636</v>
       </c>
     </row>
     <row r="298" ht="18.0" hidden="1" customHeight="1">
       <c r="A298" s="51" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="B298" s="51" t="s">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="C298" s="51" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D298" s="51" t="s">
         <v>12</v>
@@ -11277,7 +11407,7 @@
         <v>51.2667</v>
       </c>
       <c r="G298" s="51" t="s">
-        <v>600</v>
+        <v>639</v>
       </c>
       <c r="H298" s="53" t="s">
         <v>7</v>
@@ -11288,7 +11418,7 @@
     </row>
     <row r="299" ht="18.0" hidden="1" customHeight="1">
       <c r="A299" s="55" t="s">
-        <v>601</v>
+        <v>640</v>
       </c>
       <c r="B299" s="55" t="s">
         <v>305</v>
@@ -11306,7 +11436,7 @@
         <v>-156.4418</v>
       </c>
       <c r="G299" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H299" s="57" t="s">
         <v>7</v>
@@ -11317,10 +11447,10 @@
     </row>
     <row r="300" ht="18.0" hidden="1" customHeight="1">
       <c r="A300" s="55" t="s">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="B300" s="55" t="s">
-        <v>604</v>
+        <v>643</v>
       </c>
       <c r="C300" s="55" t="s">
         <v>28</v>
@@ -11335,7 +11465,7 @@
         <v>12.4964</v>
       </c>
       <c r="G300" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H300" s="57" t="s">
         <v>7</v>
@@ -11346,10 +11476,10 @@
     </row>
     <row r="301" ht="18.0" hidden="1" customHeight="1">
       <c r="A301" s="55" t="s">
-        <v>605</v>
+        <v>644</v>
       </c>
       <c r="B301" s="55" t="s">
-        <v>606</v>
+        <v>645</v>
       </c>
       <c r="C301" s="55" t="s">
         <v>65</v>
@@ -11364,7 +11494,7 @@
         <v>-84.8333</v>
       </c>
       <c r="G301" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H301" s="57" t="s">
         <v>7</v>
@@ -11375,7 +11505,7 @@
     </row>
     <row r="302" ht="18.0" hidden="1" customHeight="1">
       <c r="A302" s="55" t="s">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="B302" s="55" t="s">
         <v>174</v>
@@ -11393,7 +11523,7 @@
         <v>55.139</v>
       </c>
       <c r="G302" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H302" s="57" t="s">
         <v>7</v>
@@ -11404,7 +11534,7 @@
     </row>
     <row r="303" ht="18.0" hidden="1" customHeight="1">
       <c r="A303" s="55" t="s">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="B303" s="55" t="s">
         <v>42</v>
@@ -11422,7 +11552,7 @@
         <v>-115.1731</v>
       </c>
       <c r="G303" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H303" s="57" t="s">
         <v>7</v>
@@ -11433,7 +11563,7 @@
     </row>
     <row r="304" ht="18.0" hidden="1" customHeight="1">
       <c r="A304" s="55" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="B304" s="55" t="s">
         <v>297</v>
@@ -11451,7 +11581,7 @@
         <v>-109.9167</v>
       </c>
       <c r="G304" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H304" s="57" t="s">
         <v>7</v>
@@ -11462,13 +11592,13 @@
     </row>
     <row r="305" ht="18.0" hidden="1" customHeight="1">
       <c r="A305" s="55" t="s">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="B305" s="55" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C305" s="55" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D305" s="55" t="s">
         <v>12</v>
@@ -11480,7 +11610,7 @@
         <v>51.5167</v>
       </c>
       <c r="G305" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H305" s="57" t="s">
         <v>7</v>
@@ -11491,10 +11621,10 @@
     </row>
     <row r="306" ht="18.0" hidden="1" customHeight="1">
       <c r="A306" s="55" t="s">
-        <v>611</v>
+        <v>650</v>
       </c>
       <c r="B306" s="55" t="s">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="C306" s="55" t="s">
         <v>45</v>
@@ -11509,7 +11639,7 @@
         <v>73.3333</v>
       </c>
       <c r="G306" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H306" s="57" t="s">
         <v>7</v>
@@ -11520,10 +11650,10 @@
     </row>
     <row r="307" ht="18.0" hidden="1" customHeight="1">
       <c r="A307" s="55" t="s">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B307" s="55" t="s">
-        <v>614</v>
+        <v>653</v>
       </c>
       <c r="C307" s="55" t="s">
         <v>31</v>
@@ -11538,7 +11668,7 @@
         <v>-117.723</v>
       </c>
       <c r="G307" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H307" s="57" t="s">
         <v>7</v>
@@ -11549,7 +11679,7 @@
     </row>
     <row r="308" ht="18.0" hidden="1" customHeight="1">
       <c r="A308" s="55" t="s">
-        <v>615</v>
+        <v>654</v>
       </c>
       <c r="B308" s="55" t="s">
         <v>47</v>
@@ -11567,7 +11697,7 @@
         <v>-81.516</v>
       </c>
       <c r="G308" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H308" s="57" t="s">
         <v>7</v>
@@ -11578,7 +11708,7 @@
     </row>
     <row r="309" ht="18.0" hidden="1" customHeight="1">
       <c r="A309" s="55" t="s">
-        <v>616</v>
+        <v>655</v>
       </c>
       <c r="B309" s="55" t="s">
         <v>203</v>
@@ -11596,7 +11726,7 @@
         <v>-111.498</v>
       </c>
       <c r="G309" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H309" s="57" t="s">
         <v>7</v>
@@ -11607,7 +11737,7 @@
     </row>
     <row r="310" ht="18.0" hidden="1" customHeight="1">
       <c r="A310" s="55" t="s">
-        <v>617</v>
+        <v>656</v>
       </c>
       <c r="B310" s="55" t="s">
         <v>210</v>
@@ -11625,7 +11755,7 @@
         <v>55.95</v>
       </c>
       <c r="G310" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H310" s="57" t="s">
         <v>7</v>
@@ -11636,10 +11766,10 @@
     </row>
     <row r="311" ht="18.0" hidden="1" customHeight="1">
       <c r="A311" s="55" t="s">
-        <v>618</v>
+        <v>657</v>
       </c>
       <c r="B311" s="55" t="s">
-        <v>619</v>
+        <v>658</v>
       </c>
       <c r="C311" s="55" t="s">
         <v>50</v>
@@ -11654,7 +11784,7 @@
         <v>-87.0667</v>
       </c>
       <c r="G311" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H311" s="57" t="s">
         <v>7</v>
@@ -11665,10 +11795,10 @@
     </row>
     <row r="312" ht="18.0" hidden="1" customHeight="1">
       <c r="A312" s="55" t="s">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="B312" s="55" t="s">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="C312" s="55" t="s">
         <v>216</v>
@@ -11683,7 +11813,7 @@
         <v>55.3833</v>
       </c>
       <c r="G312" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H312" s="57" t="s">
         <v>7</v>
@@ -11694,10 +11824,10 @@
     </row>
     <row r="313" ht="18.0" hidden="1" customHeight="1">
       <c r="A313" s="55" t="s">
-        <v>622</v>
+        <v>661</v>
       </c>
       <c r="B313" s="55" t="s">
-        <v>623</v>
+        <v>662</v>
       </c>
       <c r="C313" s="55" t="s">
         <v>86</v>
@@ -11712,7 +11842,7 @@
         <v>2.1301</v>
       </c>
       <c r="G313" s="55" t="s">
-        <v>602</v>
+        <v>641</v>
       </c>
       <c r="H313" s="57" t="s">
         <v>7</v>
@@ -12412,44 +12542,83 @@
   <autoFilter ref="$A$1:$I$313">
     <filterColumn colId="8">
       <filters>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g147320-d149921-Reviews-Caribe_Hilton_Hotel-San_Juan_Puerto_Rico.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d1382900-Reviews-Hilton_Orlando-Orlando_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d1639337-Reviews-Hilton_Grand_Vacations_Club_Elara_Center_Strip_Las_Vegas-Las_Vegas_Nevada.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g60632-d23500368-Reviews-Hilton_Grand_Vacations_Club_Maui_Bay_Villas-Kihei_Maui_Hawaii.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g60608-d967966-Reviews-Hilton_Grand_Vacations_Club_Kohala_Suites_Waikoloa-Waikoloa_Kohala_Coast_Island_of_Hawai.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g34352-d88560-Reviews-Hilton_Vacation_Club_Polynesian_Isles_Kissimmee-Kissimmee_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g31187-d2521631-Reviews-Hilton_Vacation_Club_Rancho_Manana_Phoenix_Cave_Creek-Cave_Creek_Arizona.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g57097-d3606994-Reviews-Hilton_Grand_Vacations_Club_Sunrise_Lodge_Park_City-Park_City_Utah.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g297549-d308117-Reviews-Hilton_Hurghada_Plaza-Hurghada_Red_Sea_and_Sinai.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g34127-d254748-Reviews-Hilton_Vacation_Club_Mystic_Dunes_Orlando-Celebration_Orlando_Florida.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g58313-d239952-Reviews-Hilton_Vacation_Club_Greensprings_Williamsburg-Williamsburg_Virginia.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g34352-d26231990-Reviews-Embassy_Suites_by_Hilton_Orlando_Sunset_Walk-Kissimmee_Florida.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d234836-Reviews-Hilton_Grand_Vacations_Club_Paradise_Las_Vegas-Las_Vegas_Nevada.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g616286-d17573447-Reviews-Hilton_Grand_Vacations_Club_The_Crane_Barbados-Saint_Philip_Parish_Barbados.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g31310-d115484-Reviews-Arizona_Biltmore_LXR_Hotels_Resorts-Phoenix_Arizona.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g56567-d1028763-Reviews-Hilton_Dallas_Rockwall_Lakefront-Rockwall_Texas.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g1575828-d7927386-Reviews-Hilton_Yuxi_Fuxian_Lake-Chengjiang_County_Yunnan.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g4813352-d125249-Reviews-Hilton_Vacation_Club_Ridge_on_Sedona-Village_of_Oak_Creek_Arizona.html"/>
-        <filter val="—"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d813133-Reviews-Hilton_Grand_Vacations_Club_Las_Palmeras_Orlando-Orlando_Florida.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d277720-Reviews-Hilton_Grand_Vacations_Club_on_the_Las_Vegas_Strip-Las_Vegas_Nevada.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g147320-d150443-Reviews-The_Condado_Plaza_Hotel-San_Juan_Puerto_Rico.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g298564-d23331390-Reviews-ROKU_KYOTO_LXR_Hotels_Resorts-Kyoto_Kyoto_Prefecture_Kinki.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g32171-d13821720-Reviews-Hilton_Grand_Vacations_Club_MarBrisa_Carlsbad-Carlsbad_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g198581-d273504-Reviews-Hilton_Frankfurt_Gravenbruch-Neu_Isenburg_Hesse.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g26663395-d1307623-Reviews-Hilton_Grand_Vacations_Club_Parc_Soleil_Orlando-Williamsburg_Orlando_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g298063-d21327906-Reviews-Hampton_by_Hilton_Marjan_Island-Ras_Al_Khaimah_Emirate_of_Ras_Al_Khaimah.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g32847-d503504-Reviews-Hilton_Vacation_Club_Palm_Canyon_Palm_Springs-Palm_Springs_Greater_Palm_Springs_Californ.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g488116-d23118132-Reviews-Mango_House_Seychelles_LXR_Hotels_Resorts-Baie_Lazare_Mahe_Island.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g295398-d299704-Reviews-Hilton_Alexandria_Corniche-Alexandria_Alexandria_Governorate.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g60982-d1818106-Reviews-Hilton_Vacation_Club_The_Modern_Honolulu-Honolulu_Oahu_Hawaii.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d262665-Reviews-Hilton_Vacation_Club_Cypress_Pointe_Orlando-Orlando_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g34745-d86038-Reviews-Hilton_Vacation_Club_Aqua_Sol_Orlando_West-Winter_Garden_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g1080054-d12474245-Reviews-Grand_Hotel_des_Sablettes_Plage_Curio_Collection_by_Hilton-La_Seyne_sur_Mer_Var_Prov.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d217597-Reviews-Hilton_Grand_Vacations_Club_Flamingo_Las_Vegas-Las_Vegas_Nevada.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g60608-d1404166-Reviews-Hilton_Grand_Vacations_Club_Kings_Land_Waikoloa-Waikoloa_Kohala_Coast_Island_of_Hawaii_.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g297470-d11725429-Reviews-Hilton_Ningbo_Dongqian_Lake-Ningbo_Zhejiang.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g152516-d21294207-Reviews-Hilton_Grand_Vacations_Club_La_Pacifica_Los_Cabos-San_Jose_del_Cabo_Los_Cabos_Baja_Ca.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g147347-d151326-Reviews-Hilton_Vacation_Club_Royal_Palm_St_Maarten-Philipsburg_Sint_Maarten_St_Martin_St_Maarte.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g294013-d23039049-Reviews-Hilton_Abu_Dhabi_Yas_Island-Abu_Dhabi_Emirate_of_Abu_Dhabi.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d223711-Reviews-Hilton_Grand_Vacations_Club_SeaWorld_Orlando-Orlando_Florida.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g154948-d186782-Reviews-Hilton_Grand_Vacations_Club_Whistler-Whistler_British_Columbia.html"/>
-        <filter val="https://www.tripadvisor.com/Hotel_Review-g33327-d235470-Reviews-Hilton_Grand_Vacations_Club_Valdoro_Mountain_Lodge_Breckenridge-Breckenridge_Colorado.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g1190275-d23416500-Reviews-Hilton_Hotel_Tahiti-Faa_a_Tahiti_Society_Islands.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g227101-d227152-Reviews-Hilton_Malta-Saint_Julian_s_Island_of_Malta.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g297476-d300666-Reviews-Hilton_Cartagena_Hotel-Cartagena_Cartagena_District_Bolivar_Department.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g295424-d2526254-Reviews-Hilton_Dubai_The_Walk-Dubai_Emirate_of_Dubai.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g1592998-d25173962-Reviews-or20-Maysan_Doha_LXR_Hotels_Resorts-Al_Rayyan.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g58313-d239953-Reviews-Hilton_Vacation_Club_The_Historic_Powhatan_Williamsburg-Williamsburg_Virginia.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g1022639-d472114-Reviews-Hilton_Grand_Vacations_Club_Blue_Mountain_Canada-Blue_Mountains_Grey_County_Ontario.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g1219108-d887047-Reviews-Umana_Bali_LXR_Hotels_Resorts-Ungasan_Bukit_Peninsula_Bali.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g31350-d240035-Reviews-Hilton_Vacation_Club_Scottsdale_Villa_Mirage-Scottsdale_Arizona.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g152516-d652753-Reviews-Hilton_Vacation_Club_Cabo_Azul_Los_Cabos-San_Jose_del_Cabo_Los_Cabos_Baja_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g293919-d1876869-Reviews-or40-Hilton_Pattaya-Pattaya_Chonburi_Province.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g32766-d78593-Reviews-Casa_Mani_Resort_Napa_Valley_Curio_Collection_by_Hilton-Napa_Napa_Valley_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g147320-d149921-Reviews-Caribe_Hilton_Hotel-San_Juan_Puerto_Rico.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g187782-d231243-Reviews-Hilton_Sorrento_Palace-Sorrento_Province_of_Naples_Campania.html"/>
+        <filter val="https://www.hilton.com/en/hotels/sanrhol-shore-house-at-the-del/"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g294220-d26109625-Reviews-Hilton_Nanjing_Niushoushan-Nanjing_Jiangsu.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g297484-d25084426-Reviews-Hilton_Santa_Marta-Santa_Marta_Santa_Marta_Municipality_Magdalena_Department.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g298663-d20483728-Reviews-Susona_Bodrum_LXR_Hotels_Resorts-Torba_Bodrum_District_Mugla_Province_Turkish_Aegean_.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g60608-d967966-Reviews-Hilton_Grand_Vacations_Club_Kohala_Suites_Waikoloa-Waikoloa_Kohala_Coast_Island_of_Hawai.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g34352-d88560-Reviews-Hilton_Vacation_Club_Polynesian_Isles_Kissimmee-Kissimmee_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g57097-d3606994-Reviews-Hilton_Grand_Vacations_Club_Sunrise_Lodge_Park_City-Park_City_Utah.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g58313-d239952-Reviews-Hilton_Vacation_Club_Greensprings_Williamsburg-Williamsburg_Virginia.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g55711-d98731-Reviews-Hilton_Anatole-Dallas_Texas.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g297888-d308055-Reviews-Hilton_Gyeongju-Gyeongju_Gyeongsangbuk_do.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g32286-d501946-Reviews-Hilton_San_Diego_del_Mar-Del_Mar_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g295398-d7319768-Reviews-Hilton_Alexandria_King_s_Ranch-Alexandria_Alexandria_Governorate.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g8363967-d300671-Reviews-Hilton_Pyramids_Golf-6th_of_October_City_Giza_Governorate.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g34352-d26231990-Reviews-Embassy_Suites_by_Hilton_Orlando_Sunset_Walk-Kissimmee_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d234836-Reviews-Hilton_Grand_Vacations_Club_Paradise_Las_Vegas-Las_Vegas_Nevada.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g616286-d17573447-Reviews-Hilton_Grand_Vacations_Club_The_Crane_Barbados-Saint_Philip_Parish_Barbados.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g30700567-d1146058-Reviews-Hilton_Santa_Fe_Buffalo_Thunder-Cuyamungue_New_Mexico.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g30582-d14084829-Reviews-The_Lodge_At_Gulf_State_Park_A_Hilton_Hotel-Gulf_Shores_Alabama.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g294009-d19106093-Reviews-Hilton_Doha_The_Pearl-Doha.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g580307-d500716-Reviews-Hilton_Mallorca_Galatzo-Peguera_Calvia_Majorca_Balearic_Islands.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d813133-Reviews-Hilton_Grand_Vacations_Club_Las_Palmeras_Orlando-Orlando_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g45963-d277720-Reviews-Hilton_Grand_Vacations_Club_on_the_Las_Vegas_Strip-Las_Vegas_Nevada.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g294009-d25173967-Reviews-Katara_Hills_Doha_Lxr_Hotels_Resorts-Doha.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g32847-d503504-Reviews-Hilton_Vacation_Club_Palm_Canyon_Palm_Springs-Palm_Springs_Greater_Palm_Springs_Californ.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g60982-d1818106-Reviews-Hilton_Vacation_Club_The_Modern_Honolulu-Honolulu_Oahu_Hawaii.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g23869903-d217366-Reviews-Hilton_Orlando_Lake_Buena_Vista_Disney_Springs_Area-Lake_Buena_Vista_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g34515-d1308392-Reviews-Signia_By_Hilton_Orlando_An_Official_Walt_Disney_WorldR_Hotel-Orlando_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g255072-d1853238-Reviews-Hilton_Surfers_Paradise_Hotel_Residences-Surfers_Paradise_Gold_Coast_Queensland.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g32578-d218747-Reviews-Hilton_La_Jolla_Torrey_Pines-La_Jolla_San_Diego_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g60608-d1404166-Reviews-Hilton_Grand_Vacations_Club_Kings_Land_Waikoloa-Waikoloa_Kohala_Coast_Island_of_Hawaii_.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g147347-d151326-Reviews-Hilton_Vacation_Club_Royal_Palm_St_Maarten-Philipsburg_Sint_Maarten_St_Martin_St_Maarte.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g41298-d601651-Reviews-Hilton_Ocean_City_Oceanfront_Suites-Ocean_City_Maryland.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g32847-d77242-Reviews-Hilton_Palm_Springs-Palm_Springs_Greater_Palm_Springs_California.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g23869903-d85979-Reviews-Hilton_Orlando_Buena_Vista_Palace_Disney_Springs_Area-Lake_Buena_Vista_Florida.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g33327-d235470-Reviews-Hilton_Grand_Vacations_Club_Valdoro_Mountain_Lodge_Breckenridge-Breckenridge_Colorado.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Review-g294009-d2216044-Reviews-Hilton_Doha-Doha.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g31352-d225514-Reviews-Hilton_Vacation_Club_Sedona_Summit-Sedona_Arizona.html"/>
       </filters>
     </filterColumn>
@@ -12814,236 +12983,276 @@
     <hyperlink r:id="rId357" ref="H180"/>
     <hyperlink r:id="rId358" ref="I180"/>
     <hyperlink r:id="rId359" ref="H181"/>
-    <hyperlink r:id="rId360" ref="H182"/>
-    <hyperlink r:id="rId361" ref="H183"/>
-    <hyperlink r:id="rId362" ref="I183"/>
-    <hyperlink r:id="rId363" ref="H184"/>
-    <hyperlink r:id="rId364" ref="I184"/>
-    <hyperlink r:id="rId365" ref="H185"/>
-    <hyperlink r:id="rId366" ref="I185"/>
-    <hyperlink r:id="rId367" ref="H186"/>
-    <hyperlink r:id="rId368" ref="I186"/>
-    <hyperlink r:id="rId369" ref="H187"/>
-    <hyperlink r:id="rId370" ref="I187"/>
-    <hyperlink r:id="rId371" ref="H188"/>
-    <hyperlink r:id="rId372" ref="I188"/>
-    <hyperlink r:id="rId373" ref="H189"/>
-    <hyperlink r:id="rId374" ref="I189"/>
-    <hyperlink r:id="rId375" ref="H190"/>
-    <hyperlink r:id="rId376" ref="I190"/>
-    <hyperlink r:id="rId377" ref="H191"/>
-    <hyperlink r:id="rId378" ref="I191"/>
-    <hyperlink r:id="rId379" ref="H192"/>
-    <hyperlink r:id="rId380" ref="H193"/>
-    <hyperlink r:id="rId381" ref="I193"/>
-    <hyperlink r:id="rId382" ref="H194"/>
-    <hyperlink r:id="rId383" ref="I194"/>
-    <hyperlink r:id="rId384" ref="H195"/>
-    <hyperlink r:id="rId385" ref="I195"/>
-    <hyperlink r:id="rId386" ref="H196"/>
-    <hyperlink r:id="rId387" ref="I196"/>
-    <hyperlink r:id="rId388" ref="H197"/>
-    <hyperlink r:id="rId389" ref="I197"/>
-    <hyperlink r:id="rId390" ref="H198"/>
-    <hyperlink r:id="rId391" ref="I198"/>
-    <hyperlink r:id="rId392" ref="H199"/>
-    <hyperlink r:id="rId393" ref="H200"/>
-    <hyperlink r:id="rId394" ref="I200"/>
-    <hyperlink r:id="rId395" ref="H201"/>
-    <hyperlink r:id="rId396" ref="I201"/>
-    <hyperlink r:id="rId397" ref="H202"/>
-    <hyperlink r:id="rId398" ref="H203"/>
-    <hyperlink r:id="rId399" ref="H204"/>
-    <hyperlink r:id="rId400" ref="I204"/>
-    <hyperlink r:id="rId401" ref="H205"/>
-    <hyperlink r:id="rId402" ref="I205"/>
-    <hyperlink r:id="rId403" ref="H206"/>
-    <hyperlink r:id="rId404" ref="H207"/>
-    <hyperlink r:id="rId405" ref="I207"/>
-    <hyperlink r:id="rId406" ref="H208"/>
-    <hyperlink r:id="rId407" ref="I208"/>
-    <hyperlink r:id="rId408" ref="H209"/>
-    <hyperlink r:id="rId409" ref="H210"/>
-    <hyperlink r:id="rId410" ref="I210"/>
-    <hyperlink r:id="rId411" ref="H211"/>
-    <hyperlink r:id="rId412" ref="I211"/>
-    <hyperlink r:id="rId413" ref="H212"/>
-    <hyperlink r:id="rId414" ref="I212"/>
-    <hyperlink r:id="rId415" ref="H213"/>
-    <hyperlink r:id="rId416" ref="H214"/>
-    <hyperlink r:id="rId417" ref="I214"/>
-    <hyperlink r:id="rId418" ref="H215"/>
-    <hyperlink r:id="rId419" ref="I215"/>
-    <hyperlink r:id="rId420" ref="H216"/>
-    <hyperlink r:id="rId421" ref="H217"/>
-    <hyperlink r:id="rId422" ref="I217"/>
-    <hyperlink r:id="rId423" ref="H218"/>
-    <hyperlink r:id="rId424" ref="I218"/>
-    <hyperlink r:id="rId425" ref="H219"/>
-    <hyperlink r:id="rId426" ref="H220"/>
-    <hyperlink r:id="rId427" ref="H221"/>
-    <hyperlink r:id="rId428" ref="I221"/>
-    <hyperlink r:id="rId429" ref="H222"/>
-    <hyperlink r:id="rId430" ref="I222"/>
-    <hyperlink r:id="rId431" ref="H223"/>
-    <hyperlink r:id="rId432" ref="I223"/>
-    <hyperlink r:id="rId433" ref="H224"/>
-    <hyperlink r:id="rId434" ref="I224"/>
-    <hyperlink r:id="rId435" ref="H225"/>
-    <hyperlink r:id="rId436" ref="H226"/>
-    <hyperlink r:id="rId437" ref="H227"/>
-    <hyperlink r:id="rId438" ref="I227"/>
-    <hyperlink r:id="rId439" ref="H228"/>
-    <hyperlink r:id="rId440" ref="I228"/>
-    <hyperlink r:id="rId441" ref="H229"/>
-    <hyperlink r:id="rId442" ref="I229"/>
-    <hyperlink r:id="rId443" ref="H230"/>
-    <hyperlink r:id="rId444" ref="I230"/>
-    <hyperlink r:id="rId445" ref="H231"/>
-    <hyperlink r:id="rId446" ref="I231"/>
-    <hyperlink r:id="rId447" ref="H232"/>
-    <hyperlink r:id="rId448" ref="H233"/>
-    <hyperlink r:id="rId449" ref="H234"/>
-    <hyperlink r:id="rId450" ref="I234"/>
-    <hyperlink r:id="rId451" ref="H235"/>
-    <hyperlink r:id="rId452" ref="H236"/>
-    <hyperlink r:id="rId453" ref="I236"/>
-    <hyperlink r:id="rId454" ref="H237"/>
-    <hyperlink r:id="rId455" ref="I237"/>
-    <hyperlink r:id="rId456" ref="H238"/>
-    <hyperlink r:id="rId457" ref="I238"/>
-    <hyperlink r:id="rId458" ref="H239"/>
-    <hyperlink r:id="rId459" ref="I239"/>
-    <hyperlink r:id="rId460" ref="H240"/>
-    <hyperlink r:id="rId461" ref="H241"/>
-    <hyperlink r:id="rId462" ref="H242"/>
-    <hyperlink r:id="rId463" ref="H243"/>
-    <hyperlink r:id="rId464" ref="H244"/>
-    <hyperlink r:id="rId465" ref="H245"/>
-    <hyperlink r:id="rId466" ref="I245"/>
-    <hyperlink r:id="rId467" ref="H246"/>
-    <hyperlink r:id="rId468" ref="I246"/>
-    <hyperlink r:id="rId469" ref="H247"/>
-    <hyperlink r:id="rId470" ref="I247"/>
-    <hyperlink r:id="rId471" ref="H248"/>
-    <hyperlink r:id="rId472" ref="I248"/>
-    <hyperlink r:id="rId473" ref="H249"/>
-    <hyperlink r:id="rId474" ref="H250"/>
-    <hyperlink r:id="rId475" ref="I250"/>
-    <hyperlink r:id="rId476" ref="H251"/>
-    <hyperlink r:id="rId477" ref="I251"/>
-    <hyperlink r:id="rId478" ref="H252"/>
-    <hyperlink r:id="rId479" ref="I252"/>
-    <hyperlink r:id="rId480" ref="H253"/>
-    <hyperlink r:id="rId481" ref="I253"/>
-    <hyperlink r:id="rId482" ref="H254"/>
-    <hyperlink r:id="rId483" ref="H255"/>
-    <hyperlink r:id="rId484" ref="I255"/>
-    <hyperlink r:id="rId485" ref="H256"/>
-    <hyperlink r:id="rId486" ref="I256"/>
-    <hyperlink r:id="rId487" ref="H257"/>
-    <hyperlink r:id="rId488" ref="I257"/>
-    <hyperlink r:id="rId489" ref="H258"/>
-    <hyperlink r:id="rId490" ref="H259"/>
-    <hyperlink r:id="rId491" ref="H260"/>
-    <hyperlink r:id="rId492" ref="I260"/>
-    <hyperlink r:id="rId493" ref="H261"/>
-    <hyperlink r:id="rId494" ref="I261"/>
-    <hyperlink r:id="rId495" ref="H262"/>
-    <hyperlink r:id="rId496" ref="I262"/>
-    <hyperlink r:id="rId497" ref="H263"/>
-    <hyperlink r:id="rId498" ref="I263"/>
-    <hyperlink r:id="rId499" ref="H264"/>
-    <hyperlink r:id="rId500" ref="H265"/>
-    <hyperlink r:id="rId501" ref="I265"/>
-    <hyperlink r:id="rId502" ref="H266"/>
-    <hyperlink r:id="rId503" ref="I266"/>
-    <hyperlink r:id="rId504" ref="H267"/>
-    <hyperlink r:id="rId505" ref="I267"/>
-    <hyperlink r:id="rId506" ref="H268"/>
-    <hyperlink r:id="rId507" ref="I268"/>
-    <hyperlink r:id="rId508" ref="H269"/>
-    <hyperlink r:id="rId509" ref="I269"/>
-    <hyperlink r:id="rId510" ref="H270"/>
-    <hyperlink r:id="rId511" ref="I270"/>
-    <hyperlink r:id="rId512" ref="H271"/>
-    <hyperlink r:id="rId513" ref="I271"/>
-    <hyperlink r:id="rId514" ref="H272"/>
-    <hyperlink r:id="rId515" ref="I272"/>
-    <hyperlink r:id="rId516" ref="H273"/>
-    <hyperlink r:id="rId517" ref="I273"/>
-    <hyperlink r:id="rId518" ref="H274"/>
-    <hyperlink r:id="rId519" ref="I274"/>
-    <hyperlink r:id="rId520" ref="H275"/>
-    <hyperlink r:id="rId521" ref="I275"/>
-    <hyperlink r:id="rId522" ref="H276"/>
-    <hyperlink r:id="rId523" ref="H277"/>
-    <hyperlink r:id="rId524" ref="I277"/>
-    <hyperlink r:id="rId525" ref="H278"/>
-    <hyperlink r:id="rId526" ref="H279"/>
-    <hyperlink r:id="rId527" ref="H280"/>
-    <hyperlink r:id="rId528" ref="I280"/>
-    <hyperlink r:id="rId529" ref="H281"/>
-    <hyperlink r:id="rId530" ref="H282"/>
-    <hyperlink r:id="rId531" ref="I282"/>
-    <hyperlink r:id="rId532" ref="H283"/>
-    <hyperlink r:id="rId533" ref="I283"/>
-    <hyperlink r:id="rId534" ref="H284"/>
-    <hyperlink r:id="rId535" ref="H285"/>
-    <hyperlink r:id="rId536" ref="I285"/>
-    <hyperlink r:id="rId537" ref="H286"/>
-    <hyperlink r:id="rId538" ref="I286"/>
-    <hyperlink r:id="rId539" ref="H287"/>
-    <hyperlink r:id="rId540" ref="I287"/>
-    <hyperlink r:id="rId541" ref="H288"/>
-    <hyperlink r:id="rId542" ref="H289"/>
-    <hyperlink r:id="rId543" ref="H290"/>
-    <hyperlink r:id="rId544" ref="H291"/>
-    <hyperlink r:id="rId545" ref="H292"/>
-    <hyperlink r:id="rId546" ref="H293"/>
-    <hyperlink r:id="rId547" ref="H294"/>
-    <hyperlink r:id="rId548" ref="H295"/>
-    <hyperlink r:id="rId549" ref="I295"/>
-    <hyperlink r:id="rId550" ref="H296"/>
-    <hyperlink r:id="rId551" ref="I296"/>
-    <hyperlink r:id="rId552" ref="H297"/>
-    <hyperlink r:id="rId553" ref="H298"/>
-    <hyperlink r:id="rId554" ref="I298"/>
-    <hyperlink r:id="rId555" ref="H299"/>
-    <hyperlink r:id="rId556" ref="I299"/>
-    <hyperlink r:id="rId557" ref="H300"/>
-    <hyperlink r:id="rId558" ref="I300"/>
-    <hyperlink r:id="rId559" ref="H301"/>
-    <hyperlink r:id="rId560" ref="I301"/>
-    <hyperlink r:id="rId561" ref="H302"/>
-    <hyperlink r:id="rId562" ref="I302"/>
-    <hyperlink r:id="rId563" ref="H303"/>
-    <hyperlink r:id="rId564" ref="I303"/>
-    <hyperlink r:id="rId565" ref="H304"/>
-    <hyperlink r:id="rId566" ref="I304"/>
-    <hyperlink r:id="rId567" ref="H305"/>
-    <hyperlink r:id="rId568" ref="I305"/>
-    <hyperlink r:id="rId569" ref="H306"/>
-    <hyperlink r:id="rId570" ref="I306"/>
-    <hyperlink r:id="rId571" ref="H307"/>
-    <hyperlink r:id="rId572" ref="I307"/>
-    <hyperlink r:id="rId573" ref="H308"/>
-    <hyperlink r:id="rId574" ref="I308"/>
-    <hyperlink r:id="rId575" ref="H309"/>
-    <hyperlink r:id="rId576" ref="I309"/>
-    <hyperlink r:id="rId577" ref="H310"/>
-    <hyperlink r:id="rId578" ref="I310"/>
-    <hyperlink r:id="rId579" ref="H311"/>
-    <hyperlink r:id="rId580" ref="I311"/>
-    <hyperlink r:id="rId581" ref="H312"/>
-    <hyperlink r:id="rId582" ref="I312"/>
-    <hyperlink r:id="rId583" ref="H313"/>
-    <hyperlink r:id="rId584" ref="I313"/>
+    <hyperlink r:id="rId360" ref="I181"/>
+    <hyperlink r:id="rId361" ref="H182"/>
+    <hyperlink r:id="rId362" ref="I182"/>
+    <hyperlink r:id="rId363" ref="H183"/>
+    <hyperlink r:id="rId364" ref="I183"/>
+    <hyperlink r:id="rId365" ref="H184"/>
+    <hyperlink r:id="rId366" ref="I184"/>
+    <hyperlink r:id="rId367" ref="H185"/>
+    <hyperlink r:id="rId368" ref="I185"/>
+    <hyperlink r:id="rId369" ref="H186"/>
+    <hyperlink r:id="rId370" ref="I186"/>
+    <hyperlink r:id="rId371" ref="H187"/>
+    <hyperlink r:id="rId372" ref="I187"/>
+    <hyperlink r:id="rId373" ref="H188"/>
+    <hyperlink r:id="rId374" ref="I188"/>
+    <hyperlink r:id="rId375" ref="H189"/>
+    <hyperlink r:id="rId376" ref="I189"/>
+    <hyperlink r:id="rId377" ref="H190"/>
+    <hyperlink r:id="rId378" ref="I190"/>
+    <hyperlink r:id="rId379" ref="H191"/>
+    <hyperlink r:id="rId380" ref="I191"/>
+    <hyperlink r:id="rId381" ref="H192"/>
+    <hyperlink r:id="rId382" ref="I192"/>
+    <hyperlink r:id="rId383" ref="H193"/>
+    <hyperlink r:id="rId384" ref="I193"/>
+    <hyperlink r:id="rId385" ref="H194"/>
+    <hyperlink r:id="rId386" ref="I194"/>
+    <hyperlink r:id="rId387" ref="H195"/>
+    <hyperlink r:id="rId388" ref="I195"/>
+    <hyperlink r:id="rId389" ref="H196"/>
+    <hyperlink r:id="rId390" ref="I196"/>
+    <hyperlink r:id="rId391" ref="H197"/>
+    <hyperlink r:id="rId392" ref="I197"/>
+    <hyperlink r:id="rId393" ref="H198"/>
+    <hyperlink r:id="rId394" ref="I198"/>
+    <hyperlink r:id="rId395" ref="H199"/>
+    <hyperlink r:id="rId396" ref="I199"/>
+    <hyperlink r:id="rId397" ref="H200"/>
+    <hyperlink r:id="rId398" ref="I200"/>
+    <hyperlink r:id="rId399" ref="H201"/>
+    <hyperlink r:id="rId400" ref="I201"/>
+    <hyperlink r:id="rId401" ref="H202"/>
+    <hyperlink r:id="rId402" ref="I202"/>
+    <hyperlink r:id="rId403" ref="H203"/>
+    <hyperlink r:id="rId404" ref="I203"/>
+    <hyperlink r:id="rId405" ref="H204"/>
+    <hyperlink r:id="rId406" ref="I204"/>
+    <hyperlink r:id="rId407" ref="H205"/>
+    <hyperlink r:id="rId408" ref="I205"/>
+    <hyperlink r:id="rId409" ref="H206"/>
+    <hyperlink r:id="rId410" ref="I206"/>
+    <hyperlink r:id="rId411" ref="H207"/>
+    <hyperlink r:id="rId412" ref="I207"/>
+    <hyperlink r:id="rId413" ref="H208"/>
+    <hyperlink r:id="rId414" ref="I208"/>
+    <hyperlink r:id="rId415" ref="H209"/>
+    <hyperlink r:id="rId416" ref="I209"/>
+    <hyperlink r:id="rId417" ref="H210"/>
+    <hyperlink r:id="rId418" ref="I210"/>
+    <hyperlink r:id="rId419" ref="H211"/>
+    <hyperlink r:id="rId420" ref="I211"/>
+    <hyperlink r:id="rId421" ref="H212"/>
+    <hyperlink r:id="rId422" ref="I212"/>
+    <hyperlink r:id="rId423" ref="H213"/>
+    <hyperlink r:id="rId424" ref="I213"/>
+    <hyperlink r:id="rId425" ref="H214"/>
+    <hyperlink r:id="rId426" ref="I214"/>
+    <hyperlink r:id="rId427" ref="H215"/>
+    <hyperlink r:id="rId428" ref="I215"/>
+    <hyperlink r:id="rId429" ref="H216"/>
+    <hyperlink r:id="rId430" ref="I216"/>
+    <hyperlink r:id="rId431" ref="H217"/>
+    <hyperlink r:id="rId432" ref="I217"/>
+    <hyperlink r:id="rId433" ref="H218"/>
+    <hyperlink r:id="rId434" ref="I218"/>
+    <hyperlink r:id="rId435" ref="H219"/>
+    <hyperlink r:id="rId436" ref="I219"/>
+    <hyperlink r:id="rId437" ref="H220"/>
+    <hyperlink r:id="rId438" ref="I220"/>
+    <hyperlink r:id="rId439" ref="H221"/>
+    <hyperlink r:id="rId440" ref="I221"/>
+    <hyperlink r:id="rId441" ref="H222"/>
+    <hyperlink r:id="rId442" ref="I222"/>
+    <hyperlink r:id="rId443" ref="H223"/>
+    <hyperlink r:id="rId444" ref="I223"/>
+    <hyperlink r:id="rId445" ref="H224"/>
+    <hyperlink r:id="rId446" ref="I224"/>
+    <hyperlink r:id="rId447" ref="H225"/>
+    <hyperlink r:id="rId448" ref="I225"/>
+    <hyperlink r:id="rId449" ref="H226"/>
+    <hyperlink r:id="rId450" ref="I226"/>
+    <hyperlink r:id="rId451" ref="H227"/>
+    <hyperlink r:id="rId452" ref="I227"/>
+    <hyperlink r:id="rId453" ref="H228"/>
+    <hyperlink r:id="rId454" ref="I228"/>
+    <hyperlink r:id="rId455" ref="H229"/>
+    <hyperlink r:id="rId456" ref="I229"/>
+    <hyperlink r:id="rId457" ref="H230"/>
+    <hyperlink r:id="rId458" ref="I230"/>
+    <hyperlink r:id="rId459" ref="H231"/>
+    <hyperlink r:id="rId460" ref="I231"/>
+    <hyperlink r:id="rId461" ref="H232"/>
+    <hyperlink r:id="rId462" ref="I232"/>
+    <hyperlink r:id="rId463" ref="H233"/>
+    <hyperlink r:id="rId464" ref="I233"/>
+    <hyperlink r:id="rId465" ref="H234"/>
+    <hyperlink r:id="rId466" ref="I234"/>
+    <hyperlink r:id="rId467" ref="H235"/>
+    <hyperlink r:id="rId468" ref="I235"/>
+    <hyperlink r:id="rId469" ref="H236"/>
+    <hyperlink r:id="rId470" ref="I236"/>
+    <hyperlink r:id="rId471" ref="H237"/>
+    <hyperlink r:id="rId472" ref="I237"/>
+    <hyperlink r:id="rId473" ref="H238"/>
+    <hyperlink r:id="rId474" ref="I238"/>
+    <hyperlink r:id="rId475" ref="H239"/>
+    <hyperlink r:id="rId476" ref="I239"/>
+    <hyperlink r:id="rId477" ref="H240"/>
+    <hyperlink r:id="rId478" ref="I240"/>
+    <hyperlink r:id="rId479" ref="H241"/>
+    <hyperlink r:id="rId480" ref="I241"/>
+    <hyperlink r:id="rId481" ref="H242"/>
+    <hyperlink r:id="rId482" ref="I242"/>
+    <hyperlink r:id="rId483" ref="H243"/>
+    <hyperlink r:id="rId484" ref="I243"/>
+    <hyperlink r:id="rId485" ref="H244"/>
+    <hyperlink r:id="rId486" ref="I244"/>
+    <hyperlink r:id="rId487" ref="H245"/>
+    <hyperlink r:id="rId488" ref="I245"/>
+    <hyperlink r:id="rId489" ref="H246"/>
+    <hyperlink r:id="rId490" ref="I246"/>
+    <hyperlink r:id="rId491" ref="H247"/>
+    <hyperlink r:id="rId492" ref="I247"/>
+    <hyperlink r:id="rId493" ref="H248"/>
+    <hyperlink r:id="rId494" ref="I248"/>
+    <hyperlink r:id="rId495" ref="H249"/>
+    <hyperlink r:id="rId496" ref="I249"/>
+    <hyperlink r:id="rId497" ref="H250"/>
+    <hyperlink r:id="rId498" ref="I250"/>
+    <hyperlink r:id="rId499" ref="H251"/>
+    <hyperlink r:id="rId500" ref="I251"/>
+    <hyperlink r:id="rId501" ref="H252"/>
+    <hyperlink r:id="rId502" ref="I252"/>
+    <hyperlink r:id="rId503" ref="H253"/>
+    <hyperlink r:id="rId504" ref="I253"/>
+    <hyperlink r:id="rId505" ref="H254"/>
+    <hyperlink r:id="rId506" ref="I254"/>
+    <hyperlink r:id="rId507" ref="H255"/>
+    <hyperlink r:id="rId508" ref="I255"/>
+    <hyperlink r:id="rId509" ref="H256"/>
+    <hyperlink r:id="rId510" ref="I256"/>
+    <hyperlink r:id="rId511" ref="H257"/>
+    <hyperlink r:id="rId512" ref="I257"/>
+    <hyperlink r:id="rId513" ref="H258"/>
+    <hyperlink r:id="rId514" ref="I258"/>
+    <hyperlink r:id="rId515" ref="H259"/>
+    <hyperlink r:id="rId516" ref="I259"/>
+    <hyperlink r:id="rId517" ref="H260"/>
+    <hyperlink r:id="rId518" ref="I260"/>
+    <hyperlink r:id="rId519" ref="H261"/>
+    <hyperlink r:id="rId520" ref="I261"/>
+    <hyperlink r:id="rId521" ref="H262"/>
+    <hyperlink r:id="rId522" ref="I262"/>
+    <hyperlink r:id="rId523" ref="H263"/>
+    <hyperlink r:id="rId524" ref="I263"/>
+    <hyperlink r:id="rId525" ref="H264"/>
+    <hyperlink r:id="rId526" ref="I264"/>
+    <hyperlink r:id="rId527" ref="H265"/>
+    <hyperlink r:id="rId528" ref="I265"/>
+    <hyperlink r:id="rId529" ref="H266"/>
+    <hyperlink r:id="rId530" ref="I266"/>
+    <hyperlink r:id="rId531" ref="H267"/>
+    <hyperlink r:id="rId532" ref="I267"/>
+    <hyperlink r:id="rId533" ref="H268"/>
+    <hyperlink r:id="rId534" ref="I268"/>
+    <hyperlink r:id="rId535" ref="H269"/>
+    <hyperlink r:id="rId536" ref="I269"/>
+    <hyperlink r:id="rId537" ref="H270"/>
+    <hyperlink r:id="rId538" ref="I270"/>
+    <hyperlink r:id="rId539" ref="H271"/>
+    <hyperlink r:id="rId540" ref="I271"/>
+    <hyperlink r:id="rId541" ref="H272"/>
+    <hyperlink r:id="rId542" ref="I272"/>
+    <hyperlink r:id="rId543" ref="H273"/>
+    <hyperlink r:id="rId544" ref="I273"/>
+    <hyperlink r:id="rId545" ref="H274"/>
+    <hyperlink r:id="rId546" ref="I274"/>
+    <hyperlink r:id="rId547" ref="H275"/>
+    <hyperlink r:id="rId548" ref="I275"/>
+    <hyperlink r:id="rId549" ref="H276"/>
+    <hyperlink r:id="rId550" ref="I276"/>
+    <hyperlink r:id="rId551" ref="H277"/>
+    <hyperlink r:id="rId552" ref="I277"/>
+    <hyperlink r:id="rId553" ref="H278"/>
+    <hyperlink r:id="rId554" ref="I278"/>
+    <hyperlink r:id="rId555" ref="H279"/>
+    <hyperlink r:id="rId556" ref="I279"/>
+    <hyperlink r:id="rId557" ref="H280"/>
+    <hyperlink r:id="rId558" ref="I280"/>
+    <hyperlink r:id="rId559" ref="H281"/>
+    <hyperlink r:id="rId560" ref="I281"/>
+    <hyperlink r:id="rId561" ref="H282"/>
+    <hyperlink r:id="rId562" ref="I282"/>
+    <hyperlink r:id="rId563" ref="H283"/>
+    <hyperlink r:id="rId564" ref="I283"/>
+    <hyperlink r:id="rId565" ref="H284"/>
+    <hyperlink r:id="rId566" ref="I284"/>
+    <hyperlink r:id="rId567" ref="H285"/>
+    <hyperlink r:id="rId568" ref="I285"/>
+    <hyperlink r:id="rId569" ref="H286"/>
+    <hyperlink r:id="rId570" ref="I286"/>
+    <hyperlink r:id="rId571" ref="H287"/>
+    <hyperlink r:id="rId572" ref="I287"/>
+    <hyperlink r:id="rId573" ref="H288"/>
+    <hyperlink r:id="rId574" ref="I288"/>
+    <hyperlink r:id="rId575" ref="H289"/>
+    <hyperlink r:id="rId576" ref="I289"/>
+    <hyperlink r:id="rId577" ref="H290"/>
+    <hyperlink r:id="rId578" ref="I290"/>
+    <hyperlink r:id="rId579" ref="H291"/>
+    <hyperlink r:id="rId580" ref="I291"/>
+    <hyperlink r:id="rId581" ref="H292"/>
+    <hyperlink r:id="rId582" ref="I292"/>
+    <hyperlink r:id="rId583" ref="H293"/>
+    <hyperlink r:id="rId584" ref="I293"/>
+    <hyperlink r:id="rId585" ref="H294"/>
+    <hyperlink r:id="rId586" ref="I294"/>
+    <hyperlink r:id="rId587" ref="H295"/>
+    <hyperlink r:id="rId588" ref="I295"/>
+    <hyperlink r:id="rId589" ref="H296"/>
+    <hyperlink r:id="rId590" ref="I296"/>
+    <hyperlink r:id="rId591" ref="H297"/>
+    <hyperlink r:id="rId592" ref="I297"/>
+    <hyperlink r:id="rId593" ref="H298"/>
+    <hyperlink r:id="rId594" ref="I298"/>
+    <hyperlink r:id="rId595" ref="H299"/>
+    <hyperlink r:id="rId596" ref="I299"/>
+    <hyperlink r:id="rId597" ref="H300"/>
+    <hyperlink r:id="rId598" ref="I300"/>
+    <hyperlink r:id="rId599" ref="H301"/>
+    <hyperlink r:id="rId600" ref="I301"/>
+    <hyperlink r:id="rId601" ref="H302"/>
+    <hyperlink r:id="rId602" ref="I302"/>
+    <hyperlink r:id="rId603" ref="H303"/>
+    <hyperlink r:id="rId604" ref="I303"/>
+    <hyperlink r:id="rId605" ref="H304"/>
+    <hyperlink r:id="rId606" ref="I304"/>
+    <hyperlink r:id="rId607" ref="H305"/>
+    <hyperlink r:id="rId608" ref="I305"/>
+    <hyperlink r:id="rId609" ref="H306"/>
+    <hyperlink r:id="rId610" ref="I306"/>
+    <hyperlink r:id="rId611" ref="H307"/>
+    <hyperlink r:id="rId612" ref="I307"/>
+    <hyperlink r:id="rId613" ref="H308"/>
+    <hyperlink r:id="rId614" ref="I308"/>
+    <hyperlink r:id="rId615" ref="H309"/>
+    <hyperlink r:id="rId616" ref="I309"/>
+    <hyperlink r:id="rId617" ref="H310"/>
+    <hyperlink r:id="rId618" ref="I310"/>
+    <hyperlink r:id="rId619" ref="H311"/>
+    <hyperlink r:id="rId620" ref="I311"/>
+    <hyperlink r:id="rId621" ref="H312"/>
+    <hyperlink r:id="rId622" ref="I312"/>
+    <hyperlink r:id="rId623" ref="H313"/>
+    <hyperlink r:id="rId624" ref="I313"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId585"/>
+  <drawing r:id="rId625"/>
 </worksheet>
 </file>
 
@@ -13063,10 +13272,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="59" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>625</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2">
@@ -13111,7 +13320,7 @@
     </row>
     <row r="7">
       <c r="A7" s="61" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="B7" s="61">
         <f>SUM(B2:B6)</f>

--- a/public/data/hilton_resort_credit_v3.xlsx
+++ b/public/data/hilton_resort_credit_v3.xlsx
@@ -1896,7 +1896,7 @@
     <t>Shore House at The Del, LXR Hotels &amp; Resorts</t>
   </si>
   <si>
-    <t>https://www.hilton.com/en/hotels/sanrhol-shore-house-at-the-del/</t>
+    <t>https://www.tripadvisor.com/Hotel_Feature-g32250-d24043297-zft6217-Shore_House_at_The_Del_LXR_Hotels_Resorts.html</t>
   </si>
   <si>
     <t>Susona Bodrum, LXR Hotels &amp; Resorts</t>
@@ -12583,9 +12583,9 @@
         <filter val="https://www.tripadvisor.com/Hotel_Review-g32766-d78593-Reviews-Casa_Mani_Resort_Napa_Valley_Curio_Collection_by_Hilton-Napa_Napa_Valley_California.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g147320-d149921-Reviews-Caribe_Hilton_Hotel-San_Juan_Puerto_Rico.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g187782-d231243-Reviews-Hilton_Sorrento_Palace-Sorrento_Province_of_Naples_Campania.html"/>
-        <filter val="https://www.hilton.com/en/hotels/sanrhol-shore-house-at-the-del/"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g294220-d26109625-Reviews-Hilton_Nanjing_Niushoushan-Nanjing_Jiangsu.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g297484-d25084426-Reviews-Hilton_Santa_Marta-Santa_Marta_Santa_Marta_Municipality_Magdalena_Department.html"/>
+        <filter val="https://www.tripadvisor.com/Hotel_Feature-g32250-d24043297-zft6217-Shore_House_at_The_Del_LXR_Hotels_Resorts.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g298663-d20483728-Reviews-Susona_Bodrum_LXR_Hotels_Resorts-Torba_Bodrum_District_Mugla_Province_Turkish_Aegean_.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g60608-d967966-Reviews-Hilton_Grand_Vacations_Club_Kohala_Suites_Waikoloa-Waikoloa_Kohala_Coast_Island_of_Hawai.html"/>
         <filter val="https://www.tripadvisor.com/Hotel_Review-g34352-d88560-Reviews-Hilton_Vacation_Club_Polynesian_Isles_Kissimmee-Kissimmee_Florida.html"/>
